--- a/php_libs/soporte/Herramientas/temp_excel_.xlsx
+++ b/php_libs/soporte/Herramientas/temp_excel_.xlsx
@@ -16,129 +16,135 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="346">
   <si>
     <t>No Evaluado</t>
   </si>
   <si>
-    <t>ACEVEDO SERMEÑO, MADELINE ISABELLA</t>
-  </si>
-  <si>
-    <t>Cuidar de sí mismo identificando aquellas acciones, alimentos y hábitos que le generan bienestar, al mismo tiempo que incorpora algunas prácticas de reutilización de materiales y separación de desechos sólidos siempre que le sea posible, contribuyendo al cuidado colectivo de su comunidad.</t>
-  </si>
-  <si>
-    <t>Controlar los movimientos de sus manos con precisión en el desarrollo de sus actividades cotidianas.</t>
-  </si>
-  <si>
-    <t>Dominar la coordinación, velocidad y fuerza en sus movimientos al realizar juegos colaborativos y competitivos que impliquen acciones como saltar cuerda, patear y golpear pelotas o desplazarse ágilmente.</t>
-  </si>
-  <si>
-    <t>Consolidar la identificación de la lateralidad, empleando con intención su lado dominante en diferentes actividades, y reconociendo su importancia para realizar movimientos con mayor precisión.</t>
-  </si>
-  <si>
-    <t>Asociar el sonido de las letras del alfabeto con su representación gráfica, progresivamente lee palabras y textos cortos.</t>
-  </si>
-  <si>
-    <t>Escribir palabras y textos respetando la ubicación y la direccionalidad con una creciente precisión en sus trazos.</t>
-  </si>
-  <si>
-    <t>Identificar y separar los sonidos que forman una palabra, lo que le permite reconocer que las palabras están compuestas por sonidos más pequeños.</t>
-  </si>
-  <si>
-    <t>Incorporar a su repertorio expresiones y palabras nuevas, progresivamente las usa de manera intencional al comunicarse con otros o crear textos.</t>
-  </si>
-  <si>
-    <t>Expresar comprensión de los textos y diversas formas literarias al narrar una historia siguiendo su secuencia, formular y responder preguntas sobre esta.</t>
-  </si>
-  <si>
-    <t>Comprender las expresiones no verbales y la intención comunicativa de las personas, que surgen en encuentros casuales y en juegos con pares y adultos cercanos. Progresivamente, muestra intención por utilizar sus manos y algunas expresiones faciales en contextos específicos.</t>
-  </si>
-  <si>
-    <t>Narrar textos breves, reconociendo la estructura de estos, expresando sus preferencias por distintos géneros literarios como cuentos, fábulas, poemas, cómics o textos informativos. Progresivamente, comprende y describe con mayor detalle aspectos de los personajes, el escenario y el desenlace.</t>
-  </si>
-  <si>
-    <t>Escuchar con atención las ideas, puntos de vista, propuestas y situaciones de sus pares y adultos, tomando turnos en la comunicación para hacer comentarios o comunicar sus comprensiones al respecto.</t>
-  </si>
-  <si>
-    <t>Organizar juegos dramáticos en los que recrea situaciones y personajes imaginarios elaborando disfraces y escenarios.</t>
-  </si>
-  <si>
-    <t>Participar como espectador en diversas presentaciones artísticas como obras de teatro, cuentos dramatizados, shows de títeres o de sombras, desarrollando progresivamente habilidades de observación, escucha y apreciación.</t>
-  </si>
-  <si>
-    <t>Representar por medio del dibujo, modelado y pinturas sus emociones, pensamientos o experiencias cotidianas.</t>
-  </si>
-  <si>
-    <t>Apreciar las creaciones artísticas de su contexto y de otras culturas expresando lo que siente al observarlas.</t>
-  </si>
-  <si>
-    <t>Crear secuencias rítmicas combinando sonidos con instrumentos musicales o elementos del entorno, progresivamente participa en composiciones colectivas con sus pares.</t>
-  </si>
-  <si>
-    <t>Expresar su gusto musical al disfrutar sus canciones favoritas junto a sus pares y al participar en eventos sociales y culturales.</t>
-  </si>
-  <si>
-    <t>Diferenciar los sonidos que producen instrumentos de percusión, viento o cuerda mediante la exploración, la escucha atenta y la asociación con melodías o fragmentos musicales conocidos, fortaleciendo progresivamente su capacidad auditiva y su apreciación musical.</t>
-  </si>
-  <si>
-    <t>Identificar, reproducir, continuar e incorporar elementos a patrones de objetos, imágenes, sonidos o movimientos que combinan hasta tres características, magnitudes o elementos. Gradualmente, crea sus propias series, explicando la regla que sigue el patrón.</t>
-  </si>
-  <si>
-    <t>Reconocer los símbolos que representan los números cardinales del 0 al 100 y los ordinales del primero al vigésimo. Progresivamente, los escribe siguiendo la direccionalidad del trazo y utiliza el conteo de uno en uno, dos en dos, hasta de diez en diez, en situaciones cotidianas.</t>
-  </si>
-  <si>
-    <t>Componer y descomponer números hasta el 100 usando material concreto, pictórico o simbólico. Progresivamente, resuelve sumas y restas de números con total o minuendo de hasta 99, bajo acciones como: reunir, agrupar, agregar, quitar, separar o comparar, y de forma vertical.</t>
-  </si>
-  <si>
-    <t>Identificar, nombrar y clasificar líneas, figuras planas y cuerpos geométricos; de manera progresiva, construye formas más complejas a partir de figuras simples con organización espacial intencionada y descompone figuras anticipando las formas resultantes.</t>
-  </si>
-  <si>
-    <t>Comparar de manera indirecta la longitud, capacidad, volumen, superficie y peso de dos objetos utilizando elementos auxiliares. Progresivamente, utiliza instrumentos de medición convencionales como: regla, metro, cinta métrica, balanza o reloj, con mayor precisión y comprendiendo su función.</t>
-  </si>
-  <si>
-    <t>Comparar dos números del uno al 99 utilizando material concreto o pictórico. Progresivamente, ordena un conjunto de números de forma creciente o decreciente con base en su valor posicional o utilizando la recta numérica.</t>
-  </si>
-  <si>
-    <t>Realizar secuencias de más de cinco imágenes, según el orden de los eventos y actividades, utilizando los números ordinales; progresivamente, establece secuencias combinando referentes temporales, justificando el orden propuesto de manera lógica o con base en la experiencia.</t>
-  </si>
-  <si>
-    <t>Identificar la posición y orientación de objetos en su entorno o en imágenes, incluyendo las nociones espaciales de derecha e izquierda. Progresivamente, representa la posición de los objetos de forma pictórica y brinda indicaciones de posición y direccionalidad.</t>
-  </si>
-  <si>
-    <t>Seguir instrucciones de pasos para completar actividades de programación básica. De forma progresiva, las planifica y mejora de manera autónoma, utilizando aplicaciones y recursos digitales apropiados para su edad.</t>
-  </si>
-  <si>
-    <t>Planificar y ejecutar estrategias para resolver problemas cotidianos en colaboración con sus pares, incluyendo paulatinamente la creación y mejora de herramientas o dispositivos, con acompañamiento del adulto.</t>
-  </si>
-  <si>
-    <t>Explorar y comprender la función de objetos, herramientas, dispositivos o aplicaciones cada vez más complejos. Progresivamente, justifica de manera coherente su uso en función de objetivos o problemas específicos.</t>
-  </si>
-  <si>
-    <t>Explicar los cambios, comportamientos y reacciones que observa en los elementos de la naturaleza, objetos y fenómenos naturales, comenzando a establecer conexiones causales. Poco a poco, los registra combinando representaciones gráficas y frases cortas.</t>
-  </si>
-  <si>
-    <t>Verificar sus hipótesis por medio de diferentes estrategias siguiendo un orden secuencial. Gradualmente, cambia o replantea sus acciones o estrategias con el propósito de obtener resultados más cercanos a lo planteado inicialmente.</t>
-  </si>
-  <si>
-    <t>Comprender los fenómenos físicos y naturales de su entorno a través de la observación y experimentación, lo que le permite gradualmente identificar patrones y realizar conexiones entre la causa y el efecto.</t>
-  </si>
-  <si>
-    <t>Comprender y apropiar acuerdos y normas de convivencia que regulan el comportamiento individual y grupal en diferentes contextos, como la escuela, el hogar y la comunidad, lo que les permite internalizar valores como el respeto, honestidad y responsabilidad.</t>
-  </si>
-  <si>
-    <t>Participar en la organización de actividades grupales, mostrando iniciativa y disposición para asumir roles dentro del grupo. Progresivamente, desarrolla una comprensión del trabajo en equipo, incluyendo la identificación de conflictos, sus causas y la búsqueda de soluciones.</t>
-  </si>
-  <si>
-    <t>Reconocer sus emociones como la vergüenza, la culpa, la empatía y la gratitud. Paulatinamente, se muestra más resiliente ante los fracasos, las dificultades y las críticas.</t>
-  </si>
-  <si>
-    <t>Construir relaciones de amistad en las que busca aprobación, apoyo y complicidad por parte de sus pares durante el juego cooperativo y otras actividades cotidianas. Progresivamente, establece criterios personales para elegir a sus amistades, basados en intereses comunes, afinidades y formas de relacionarse.</t>
-  </si>
-  <si>
-    <t>Participar en la toma de decisiones sobre asuntos que le interesan y le afectan, tanto en el hogar como en el entorno educativo, lo que le permite desarrollar progresivamente un sentido de pertenencia y la capacidad de influir en su entorno.</t>
-  </si>
-  <si>
-    <t>Adquirir una conciencia cada vez mayor de su cultura y del territorio en el que crece, lo cual contribuye a la construcción de su identidad personal, social y cultural.</t>
+    <t>AVILA LINARES, EMILY NATASHA</t>
+  </si>
+  <si>
+    <t>Controlar su cuerpo al realizar desplazamientos por el espacio explorando cambios de direcciones que contribuye a una creciente orientación en su entorno.</t>
+  </si>
+  <si>
+    <t>Reconocer el sonido de las vocales presentes en su nombre y en palabras familiares, mostrando gradualmente la intención de incorporar trazos similares a estas en sus grafías.</t>
+  </si>
+  <si>
+    <t>Coordinar movimientos como saltar sobre obstáculos, caminar en puntillas o correr sobre líneas o marcas en el piso. Progresivamente, logra lanzar un objeto hacia un objetivo y atraparlo con ambas manos.</t>
+  </si>
+  <si>
+    <t>Reconocer que las frases y oraciones están formadas por palabras individuales. Paulatinamente, identifica palabras que riman y las separa en sílabas de forma oral con apoyos rítmicos como aplausos o zapateos.</t>
+  </si>
+  <si>
+    <t>Coordinar y controlar movimientos con mayor precisión en actividades cotidianas como revolver, limpiar, enroscar, cortar con tijera, ensartar, encajar o usar colores.</t>
+  </si>
+  <si>
+    <t>Realizar acciones que demuestren conciencia de sus necesidades y mayor interés para satisfacerlas, intentando cuidar de sí mismo con menos apoyo de sus cuidadores. Gradualmente, logra identificar qué actividades le generan bienestar.</t>
+  </si>
+  <si>
+    <t>Ampliar su vocabulario incorporando palabras nuevas que escucha. Progresivamente, las utiliza espontáneamente en conversaciones o para describir acciones, objetos y emociones en diferentes contextos.</t>
+  </si>
+  <si>
+    <t>Disfrutar de la lectura de cuentos e historias, siguiendo con la mirada o con su dedo y, progresivamente, hace predicciones a partir de las imágenes y los títulos de estos.</t>
+  </si>
+  <si>
+    <t>Imitar aquellas expresiones corporales de adultos cercanos que utiliza para responder a normas que se siguen en ciertas situaciones grupales o en pares. Eventualmente, los gestos y expresiones que imita los adopta como propios en su forma de expresarse en sus relaciones sociales.</t>
+  </si>
+  <si>
+    <t>Demostrar mayor entendimiento de expresiones no verbales, particularmente miradas, gestos y posturas al interactuar con otras personas; paulatinamente, comprende el uso de expresiones corporales en situaciones comunicativas.</t>
+  </si>
+  <si>
+    <t>Describir personas y acontecimientos usando palabras para resaltar algunas de las características que llaman su atención. Progresivamente, recurre a nuevo vocabulario y a estructuras sintácticas más complejas mediante las cuales brinda explicaciones más detalladas.</t>
+  </si>
+  <si>
+    <t>Disfrutar de juegos vocálicos y consonánticos en los que memoriza onomatopeyas, rondas, canciones, rimas y trabalenguas para, progresivamente, jugar con las palabras al crear nuevas y explorar reglas gramaticales más complejas.</t>
+  </si>
+  <si>
+    <t>Participar en el desarrollo de juegos simbólicos en los que improvisa; crea historias, escenarios, personajes y anima objetos junto a sus pares.</t>
+  </si>
+  <si>
+    <t>Disfrutar al personificar a sus personajes preferidos durante el juego, imitando las voces, posturas y acciones característicos de estos; progresivamente, recrean historias fantásticas con sus pares.</t>
+  </si>
+  <si>
+    <t>Apreciar los detalles de los elementos que encuentra en la naturaleza y en su entorno para, posteriormente, intentar representarlos a través de dibujos, modelados y otras expresiones plásticas que son de su interés.</t>
+  </si>
+  <si>
+    <t>Mostrar interés por las expresiones plásticas propias y de los demás, para posteriormente apreciar diversas expresiones visuales y plásticas propias de su cultura.</t>
+  </si>
+  <si>
+    <t>Reconocer algunas de las cualidades del sonido como tonos graves y agudos, fuertes y suaves, así como los silencios que experimentan en los juegos rítmicos. Progresivamente, asocia los sonidos con algunas imágenes que los representan.</t>
+  </si>
+  <si>
+    <t>Mostrar interés en llevar el pulso de las canciones con su cuerpo, poco a poco explora el ritmo y la melodía de estas.</t>
+  </si>
+  <si>
+    <t>Relacionar los sonidos que escucha con lugares, animales, objetos o situaciones, lo que progresivamente le permite apreciar los paisajes sonoros que se encuentran en su entorno.</t>
+  </si>
+  <si>
+    <t>Crear series de objetos o imágenes con base en una o dos características o magnitudes. Progresivamente, continúa series siguiendo un patrón ya establecido con base en una característica.</t>
+  </si>
+  <si>
+    <t>Contar de uno en uno los objetos de un conjunto de hasta diez elementos, iniciando en uno. Gradualmente, reconoce el nombre y símbolo de los números hasta el diez, imitando el trazo con poca precisión y los utiliza en actividades cotidianas que involucran dinero.</t>
+  </si>
+  <si>
+    <t>Componer y descomponer grupos de tres a cinco objetos de forma intuitiva. De manera progresiva, realiza estas acciones con conjuntos de hasta diez elementos, utilizando el conteo de uno en uno para identificar el total de objetos en los grupos formados.</t>
+  </si>
+  <si>
+    <t>Identificar y clasificar líneas, figuras y cuerpos geométricos presentes en su entorno; gradualmente, los utiliza en actividades cotidianas como emparejar piezas, construir estructuras o armar rompecabezas.</t>
+  </si>
+  <si>
+    <t>Realizar comparación directa de longitud, peso, tamaño, capacidad y volumen de dos objetos, introduciendo gradualmente la exploración de instrumentos de medición convencionales. Poco a poco, realiza la comparación indirecta de la longitud de dos objetos utilizando como unidad de medida partes de su cuerpo, como sus manos o pies.</t>
+  </si>
+  <si>
+    <t>Comparar la cantidad de objetos de dos conjuntos, llegando a expresar progresivamente si un conjunto tiene más o menos elementos, o si tiene la misma cantidad.</t>
+  </si>
+  <si>
+    <t>Comprender algunas expresiones relacionadas con el tiempo, utilizándolas progresivamente para secuenciar tres actividades o imágenes atendiendo a un orden lógico y cronológico.</t>
+  </si>
+  <si>
+    <t>Clasificar objetos combinando hasta dos características. De manera progresiva, resolverá problemas relacionados con la clasificación, como organizar objetos de manera eficiente para completar una tarea o juego específico, o identificar elementos agregados incorrectamente a una colección o serie de objetos.</t>
+  </si>
+  <si>
+    <t>Reconocer la posición de algunos objetos con respecto a otros, logrando progresivamente expresar la posición de la mayoría de los objetos de su entorno.</t>
+  </si>
+  <si>
+    <t>Seguir pasos que le indica el adulto para preparar recetas, construir estructuras y aparatos; gradualmente, sigue secuencias simples de múltiples pasos de manera más independiente.</t>
+  </si>
+  <si>
+    <t>Analizar problemas que se le presentan en la vida cotidiana, identificando algunas variables y puntos clave. Progresivamente, planifica y ejecuta estrategias para intentar solucionarlos de forma más eficiente.</t>
+  </si>
+  <si>
+    <t>Explorar objetos y dispositivos tecnológicos mediante diversas acciones para descubrir su utilidad y funcionamiento; poco a poco, busca información que le permita comprenderlos con mayor profundidad.</t>
+  </si>
+  <si>
+    <t>Consolidar la habilidad de prever las consecuencias de sus acciones mediante la relación causa-efecto, haciendo relaciones más abstractas de anticipación basadas en sus conocimientos y experiencias previas.</t>
+  </si>
+  <si>
+    <t>Realizar preguntas sobre la naturaleza, los fenómenos físico-naturales y el funcionamiento del cuerpo de los seres humanos, con la finalidad de comprender el porqué de los acontecimientos, expresando sus comprensiones por medio de explicaciones y, poco a poco, por medio de ilustraciones.</t>
+  </si>
+  <si>
+    <t>Comprobar sus hipótesis al ejercer la misma secuencia de acciones varias veces; de forma paulatina, comprende que los objetos y elementos del entorno tienen diferentes propiedades y características que les identifican a cada uno, logrando establecer algunas conclusiones sencillas.</t>
+  </si>
+  <si>
+    <t>Explorar objetos y elementos naturales del entorno; poco a poco, ejerce ciertas acciones que le permiten descubrir cambios, propiedades y cualidades de estos.</t>
+  </si>
+  <si>
+    <t>Resolver conflictos apoyado en los adultos. De forma paulatina, lo realiza de manera autónoma llegando a acuerdos con sus pares.</t>
+  </si>
+  <si>
+    <t>Establecer acuerdos con sus pares para la organización de juegos, celebraciones, materiales y espacios; gradualmente, se apropia de normas de convivencia.</t>
+  </si>
+  <si>
+    <t>Identificar las causas y consecuencias de sus reacciones y acciones, incorporando progresivamente estrategias para recuperar la calma, regular sus emociones y apoyar a otros cuando están tristes o molestos.</t>
+  </si>
+  <si>
+    <t>Establecer relaciones con pares y adultos en diferentes contextos a partir de conversaciones y al involucrarse en juegos de roles sociales. Progresivamente, comparte espacios, juguetes, materiales y objetos con aquellas personas que considera cercanas.</t>
+  </si>
+  <si>
+    <t>Participar en diferentes tipos de juegos y actividades en los que asume diversos roles sociales, recreando situaciones que le ayudan a comprender y practicar su creciente independencia y toma de decisiones.</t>
+  </si>
+  <si>
+    <t>Reconocer que posee características físicas, habilidades y preferencias diferentes y similares a sus pares; progresivamente, esto contribuye con el fortalecimiento de su identidad personal y social.</t>
   </si>
   <si>
     <t>Nombre del Alumno</t>
@@ -147,79 +153,40 @@
     <t>Código NIE</t>
   </si>
   <si>
-    <t>Alvarado Santos, Leilany Rebeca</t>
-  </si>
-  <si>
-    <t>ASENCIO GONZALEZ, JARED GABRIEL</t>
-  </si>
-  <si>
-    <t>BELTRAN BELTRAN, JOHAN CAMILO</t>
-  </si>
-  <si>
-    <t>BELTRAN BELTRAN, KILIAN OSMAR</t>
-  </si>
-  <si>
-    <t>CABRERA MARTÍNEZ, ALEJANDRO MAURICIO</t>
-  </si>
-  <si>
-    <t>CALDERON LOPEZ, DYLAN EZEQUIEL</t>
-  </si>
-  <si>
-    <t>CALIDONIO CRUZ, RONALD GEOVANNY</t>
-  </si>
-  <si>
-    <t>CHAVEZ AZAMA, ISAAC ALEXANDER</t>
-  </si>
-  <si>
-    <t>CHAVEZ RECINOS, JORGE ANDRE</t>
-  </si>
-  <si>
-    <t>ESCARATE MARTÍNEZ, GÉNESIS DAMARIS</t>
-  </si>
-  <si>
-    <t>GONAZALEZ LEIVA, WENDY ZULEYMA</t>
-  </si>
-  <si>
-    <t>JACO HERRERA, MICHAEL GAEL</t>
-  </si>
-  <si>
-    <t>MURILLO DIAZ, PRISCILA VICTORIA</t>
-  </si>
-  <si>
-    <t>PALMA VASQUEZ, MATEO EZEQUIEL</t>
-  </si>
-  <si>
-    <t>POLANCO IRAHETA, AXEL ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAMIREZ MANCIA, LUCAS ANTONIO</t>
-  </si>
-  <si>
-    <t>RECINOS MENDEZ, VALENTINA NICOLE</t>
-  </si>
-  <si>
-    <t>RIVAS FLORES, JOSUE CALEB</t>
-  </si>
-  <si>
-    <t>SANTOS CRUZ, JOSE ISAI</t>
-  </si>
-  <si>
-    <t>SANTOS DE LA CRUZ, MATTHEW ALESSANDRO</t>
-  </si>
-  <si>
-    <t>SIGUENZA CARIAS, JOSE ALEXANDER</t>
-  </si>
-  <si>
-    <t>SOLIS COLOCHO, NATALIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>VALDES VEGA, ALISSON SAMANTA</t>
-  </si>
-  <si>
-    <t>VALDEZ MARTÍNEZ, DENIS ULISES</t>
-  </si>
-  <si>
-    <t>ZARCEÑO HERRERA, KIMBERLY ROXANA</t>
+    <t>BATRES BARILLAS, ERIC JOE</t>
+  </si>
+  <si>
+    <t>GARCÍA HERNÁNDEZ, ANDERSON EDUARDO</t>
+  </si>
+  <si>
+    <t>GONZÁLEZ MUNDO, ABNER YAHIR</t>
+  </si>
+  <si>
+    <t>HERNÁNDEZ MARTÍNEZ, JEREMY JAREL</t>
+  </si>
+  <si>
+    <t>HERNÁNDEZ MENÉNDEZ, CRISTIAN ANTONIO</t>
+  </si>
+  <si>
+    <t>HERNÁNDEZ RAMÍREZ, ILIANA RAQUEL</t>
+  </si>
+  <si>
+    <t>MARTÍNEZ GUERRA, ANGELA ANTONIA</t>
+  </si>
+  <si>
+    <t>ORELLANA MURCIA, SANTIAGO ESTEBAN</t>
+  </si>
+  <si>
+    <t>PORTILLO GARCÍA, MAYENSI AYLIN</t>
+  </si>
+  <si>
+    <t>RAMOS MÉNDEZ, SHEILA NAZARETH</t>
+  </si>
+  <si>
+    <t>SILIEZAR CHILIN, EITHAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>VILLANUEVA ALARCON, KELVIN STANLEY</t>
   </si>
   <si>
     <t>ID</t>
@@ -228,823 +195,865 @@
     <t>Indicador</t>
   </si>
   <si>
-    <t>DP1-PG-01-A</t>
-  </si>
-  <si>
-    <t>Se describe a sí mismo detallando aspectos de su personalidad, habilidades, intereses y valores.</t>
-  </si>
-  <si>
-    <t>DP1-PG-01-B</t>
-  </si>
-  <si>
-    <t>Diferencia los grupos a los que pertenece identificando los diversos roles sociales, actividades y prácticas culturales que se llevan a cabo en cada uno.</t>
-  </si>
-  <si>
-    <t>DP1-PG-01-C</t>
-  </si>
-  <si>
-    <t>Participa en festividades, actividades familiares y sociales, poniendo en práctica sus valores, normas y formas de relacionarse con pares y adultos, de acuerdo con sus principios morales y creencias.</t>
-  </si>
-  <si>
-    <t>DP1-PG-01-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-02-A</t>
-  </si>
-  <si>
-    <t>Realiza tareas escolares y domésticas demostrando capacidad para seguir instrucciones, comprometerse y completar los proyectos que inicia.</t>
-  </si>
-  <si>
-    <t>DP1-PG-02-B</t>
-  </si>
-  <si>
-    <t>Comprende que sus actuaciones, elecciones y comportamientos tienen reacciones y consecuencias.</t>
-  </si>
-  <si>
-    <t>DP1-PG-02-C</t>
-  </si>
-  <si>
-    <t>Reflexiona sobre su propio comportamiento y actuación en diferentes momentos y espacios; esto contribuye a la autorreflexión y autorregulación.</t>
-  </si>
-  <si>
-    <t>DP1-PG-02-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-03-A</t>
-  </si>
-  <si>
-    <t>Fortalece los lazos de amistad sintiéndose valorado por sus pares al participar en actividades como: pasar tiempo juntos, jugar, explorar el entorno, entre otros.</t>
-  </si>
-  <si>
-    <t>DP1-PG-03-B</t>
-  </si>
-  <si>
-    <t>Comparte intereses, juegos y actividades con algunos pares, con quienes inicia relaciones de amistad basadas en gustos, afinidades y experiencias comunes.</t>
-  </si>
-  <si>
-    <t>DP1-PG-03-C</t>
-  </si>
-  <si>
-    <t>Establece lazos de amistad al sentirse valorado por sus pares y al participar en juegos cooperativos, conversaciones y actividades compartidas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-03-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-04-A</t>
-  </si>
-  <si>
-    <t>Reflexiona sobre sus propias emociones y cómo estas influyen en sus pensamientos, comportamientos y relaciones.</t>
-  </si>
-  <si>
-    <t>DP1-PG-04-B</t>
-  </si>
-  <si>
-    <t>Mantiene la calma ante situaciones desafiantes, estresantes o frustrantes, así como ante las reacciones poco asertivas de sus pares.</t>
-  </si>
-  <si>
-    <t>DP1-PG-04-C</t>
-  </si>
-  <si>
-    <t>Utiliza estrategias para regular sus emociones, incluyendo técnicas de relajación, autocontrol, pensamiento positivo y comprendiendo los sentimientos y necesidades de los demás.</t>
-  </si>
-  <si>
-    <t>DP1-PG-04-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-05-A</t>
-  </si>
-  <si>
-    <t>Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-05-B</t>
-  </si>
-  <si>
-    <t>Toma iniciativa para proponer, organizar y liderar juegos o proyectos grupales, asignando roles y promoviendo la participación de sus compañeros.</t>
-  </si>
-  <si>
-    <t>DP1-PG-05-C</t>
-  </si>
-  <si>
-    <t>Identifica situaciones de conflicto y actúa de manera autónoma para buscar soluciones, considerando las causas y consecuencias de sus acciones.</t>
-  </si>
-  <si>
-    <t>DP1-PG-05-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-06-A</t>
-  </si>
-  <si>
-    <t>Comprende los acuerdos y normas de convivencia de manera consistente, aplicándolas en diferentes contextos sin ayuda del adulto.</t>
-  </si>
-  <si>
-    <t>DP1-PG-06-B</t>
-  </si>
-  <si>
-    <t>Aplica los acuerdos y las normas de manera consistente, regulando su comportamiento en diferentes entornos en los que pone en práctica los valores del respeto, honestidad y responsabilidad.</t>
-  </si>
-  <si>
-    <t>DP1-PG-06-C</t>
-  </si>
-  <si>
-    <t>Apropia los acuerdos y las normas de convivencia como parte importante para la regulación del comportamiento social y la cultura ciudadana.</t>
-  </si>
-  <si>
-    <t>DP1-PG-06-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-07-A</t>
-  </si>
-  <si>
-    <t>Observa fenómenos físicos y naturales como el clima, el ciclo del agua, los cambios en el crecimiento de las plantas, los animales, así como la luz y la sombra a lo largo del día, entre otros.</t>
-  </si>
-  <si>
-    <t>DP1-PG-07-B</t>
-  </si>
-  <si>
-    <t>Describe los patrones y las conexiones existentes entre los fenómenos físicos y naturales relacionados con el estado del tiempo, el ciclo del agua, los cambios en la luz y la sombra a lo largo del día, entre otros.</t>
-  </si>
-  <si>
-    <t>DP1-PG-07-C</t>
-  </si>
-  <si>
-    <t>Explica los cambios y transformaciones del entorno, estableciendo relaciones causa-efecto, utilizando vocabulario cada vez más elaborado y de forma más detallada.</t>
-  </si>
-  <si>
-    <t>DP1-PG-07-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-08-A</t>
-  </si>
-  <si>
-    <t>Realiza acciones de forma secuencial y con intención para comprobar sus ideas, reconociendo el ensayo y error como parte del proceso para verificar lo que piensa o imagina.</t>
-  </si>
-  <si>
-    <t>DP1-PG-08-B</t>
-  </si>
-  <si>
-    <t>Prueba diferentes estrategias para obtener los resultados esperados de acuerdo con las hipótesis planteadas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-08-C</t>
-  </si>
-  <si>
-    <t>Realiza cambios de estrategia o ajusta sus acciones con la finalidad de comprobar, replantear o desestimar sus hipótesis.</t>
-  </si>
-  <si>
-    <t>DP1-PG-08-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-09-A</t>
-  </si>
-  <si>
-    <t>Recolecta información sobre los fenómenos, objetos y elementos de la naturaleza, con el fin de establecer la causa de los cambios, comportamientos y reacciones que observa.</t>
-  </si>
-  <si>
-    <t>DP1-PG-09-B</t>
-  </si>
-  <si>
-    <t>Comunica sus preguntas, argumentos y explicaciones sobre los cambios, fenómenos y relaciones entre causa y efecto que observa, utilizando conceptos y vocabulario científico que ha aprendido.</t>
-  </si>
-  <si>
-    <t>DP1-PG-09-C</t>
-  </si>
-  <si>
-    <t>Representa, combinando ilustraciones, esquemas, fotografías y textos cortos, los fenómenos físicos y naturales que observa, evidenciando las conexiones entre causa y efecto.</t>
-  </si>
-  <si>
-    <t>DP1-PG-09-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-10-A</t>
-  </si>
-  <si>
-    <t>Explora funciones de dispositivos más avanzados y complejos, como sistemas de audio y video.</t>
-  </si>
-  <si>
-    <t>DP1-PG-10-B</t>
-  </si>
-  <si>
-    <t>Selecciona objetos, dispositivos tecnológicos, aplicaciones o herramientas que son de utilidad para alcanzar objetivos o realizar labores específicas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-10-C</t>
-  </si>
-  <si>
-    <t>Explica de manera coherente la selección de un objeto, herramienta, dispositivo o aplicación para la solución de problemas, con base en la causa y efecto.</t>
-  </si>
-  <si>
-    <t>DP1-PG-10-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-11-A</t>
-  </si>
-  <si>
-    <t>Planifica estrategias en colaboración con sus pares para resolver una necesidad concreta, identificando herramientas o dispositivos que se pueden crear para ese fin.</t>
-  </si>
-  <si>
-    <t>DP1-PG-11-B</t>
-  </si>
-  <si>
-    <t>Construye el prototipo de aparatos y estructuras con los cuales se resuelva alguna situación o problema de la vida cotidiana, identificando limitaciones o fallas en su funcionamiento.</t>
-  </si>
-  <si>
-    <t>DP1-PG-11-C</t>
-  </si>
-  <si>
-    <t>Modifica y mejora sus creaciones con base en las fallas o limitaciones en su funcionamiento, con apoyo del adulto.</t>
-  </si>
-  <si>
-    <t>DP1-PG-11-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-12-A</t>
-  </si>
-  <si>
-    <t>Sigue instrucciones paso a paso para realizar actividades de programación básica en juegos o aplicaciones educativas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-12-B</t>
-  </si>
-  <si>
-    <t>Crea o modifica sus proyectos de programación aplicando conceptos básicos como secuencias o repeticiones.</t>
-  </si>
-  <si>
-    <t>DP1-PG-12-C</t>
-  </si>
-  <si>
-    <t>Explica con sus propias palabras o de manera gráfica cómo organizó las acciones en su proyecto, justificando algunas decisiones que tomó al programar o resolver un problema.</t>
-  </si>
-  <si>
-    <t>DP1-PG-12-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-13-A</t>
-  </si>
-  <si>
-    <t>Identifica la orientación de objetos de su entorno e imágenes, nombrándolas como: vertical, horizontal o inclinada.</t>
-  </si>
-  <si>
-    <t>DP1-PG-13-B</t>
-  </si>
-  <si>
-    <t>Identifica la posición de los objetos respecto a otro objeto o a su cuerpo, incluyendo las nociones espaciales de izquierda y derecha, tomando en cuenta la perspectiva del punto de referencia.</t>
-  </si>
-  <si>
-    <t>DP1-PG-13-C</t>
-  </si>
-  <si>
-    <t>Representa la posición de los objetos de forma pictórica y brinda indicaciones de posición y direccionalidad.</t>
-  </si>
-  <si>
-    <t>DP1-PG-13-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-14-A</t>
-  </si>
-  <si>
-    <t>Reconoce y utiliza los números ordinales para describir el orden de acciones o eventos en situaciones cotidianas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-14-B</t>
-  </si>
-  <si>
-    <t>Organiza más de cinco actividades o imágenes de forma lógica, combinando números ordinales y expresiones temporales como: por la mañana, por la tarde, por la noche, antes, primero, después, entre otras.</t>
-  </si>
-  <si>
-    <t>DP1-PG-14-C</t>
-  </si>
-  <si>
-    <t>Reconoce el orden y organiza de forma cronológica los hechos que ocurren en una historia o cuento que lee o escucha, combinando con precisión números ordinales y referentes temporales, justificando el orden propuesto con base en su experiencia o la lógica.</t>
-  </si>
-  <si>
-    <t>DP1-PG-14-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-15-A</t>
-  </si>
-  <si>
-    <t>Compara dos números del uno al 99 asociándolos a la cantidad que representan, utilizando material concreto o pictórico, o empleando la recta numérica.</t>
-  </si>
-  <si>
-    <t>DP1-PG-15-B</t>
-  </si>
-  <si>
-    <t>Reconoce el valor posicional de las cifras de los números del uno al 99 y lo utiliza para hacer comparaciones.</t>
-  </si>
-  <si>
-    <t>DP1-PG-15-C</t>
-  </si>
-  <si>
-    <t>Utiliza la comparación para ordenar un conjunto de números de forma creciente o decreciente.</t>
-  </si>
-  <si>
-    <t>DP1-PG-15-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-16-A</t>
-  </si>
-  <si>
-    <t>Compara magnitudes10 como longitud, capacidad, volumen, superficie y peso utilizando recipientes, bloques u otros objetos auxiliares, justificando la unidad de medida utilizada y la estrategia con base en la magnitud a comparar.</t>
-  </si>
-  <si>
-    <t>DP1-PG-16-B</t>
-  </si>
-  <si>
-    <t>Utiliza instrumentos convencionales como regla, cinta métrica, metro, balanza, báscula o termómetro de manera intencionada para medir o comprobar estimaciones de manera más precisa.</t>
-  </si>
-  <si>
-    <t>DP1-PG-16-C</t>
-  </si>
-  <si>
-    <t>Realiza la lectura del reloj análogo en hora en punto, la hora y media, hora y minutos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-16-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-17-A</t>
-  </si>
-  <si>
-    <t>Identifica, nombra y clasifica líneas, figuras y cuerpos geométricos como la forma de triángulo, forma de círculo, forma de cuadrado, forma de rectángulo, forma de óvalo, línea recta, línea curva, línea quebrada, línea mixta, línea abierta, línea cerrada, forma de esfera, forma de cilindro, forma de prisma, forma de cubo, entre otras.</t>
-  </si>
-  <si>
-    <t>DP1-PG-17-B</t>
-  </si>
-  <si>
-    <t>Traza líneas y construye figuras y cuerpos geométricos complejos combinando formas básicas con organización espacial intencionada, como representar un castillo o una cuidad utilizando material concreto, trazos o recortes.</t>
-  </si>
-  <si>
-    <t>DP1-PG-17-C</t>
-  </si>
-  <si>
-    <t>Descompone figuras geométricas en partes más pequeñas, anticipando las formas resultantes y explicando cómo están compuestas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-17-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-18-A</t>
-  </si>
-  <si>
-    <t>Realiza la composición y descomposición de un número hasta el 100 utilizando material concreto, pictórico, billetes o monedas, incluyendo la descomposición del número en decenas y unidades.</t>
-  </si>
-  <si>
-    <t>DP1-PG-18-B</t>
-  </si>
-  <si>
-    <t>Realiza sumas y restas con totales o minuendo hasta 99, bajo las acciones de agrupar, reunir, agregar, o separar, quitar y comparar, logrando progresivamente realizar cálculos verticales de suma y resta sin llevar ni prestar.</t>
-  </si>
-  <si>
-    <t>DP1-PG-18-C</t>
-  </si>
-  <si>
-    <t>Encuentra un sumando desconocido en una suma y el minuendo o sustraendo desconocido en una resta de dos números hasta 20, a través del ensayo y error, utilizando material concreto o pictórico.</t>
-  </si>
-  <si>
-    <t>DP1-PG-18-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-19-A</t>
-  </si>
-  <si>
-    <t>Identifica los símbolos que representan a los números cardinales del 0 al 100 y los números ordinales del primero al vigésimo.</t>
-  </si>
-  <si>
-    <t>DP1-PG-19-B</t>
-  </si>
-  <si>
-    <t>Escribe los símbolos que representan a los números cardinales del 0 al 100 y los números ordinales del primero al vigésimo, respetando la direccionalidad del trazo.</t>
-  </si>
-  <si>
-    <t>DP1-PG-19-C</t>
-  </si>
-  <si>
-    <t>Realiza conteo de uno en uno, de dos en dos, de tres en tres, de cuatro en cuatro, de cinco en cinco hasta de diez en diez, iniciando en cualquier número y hasta llegar a 100, usándolos para resolver situaciones de la vida cotidiana.</t>
-  </si>
-  <si>
-    <t>DP1-PG-19-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-20-A</t>
-  </si>
-  <si>
-    <t>Identifica y reproduce patrones de objetos, imágenes, sonidos o movimientos que combinan hasta tres características, magnitudes o elementos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-20-B</t>
-  </si>
-  <si>
-    <t>Continúa e incorpora elementos a series de objetos o imágenes que combinen hasta tres características o magnitudes, incluyendo cambios de orientación, identificando la regla del patrón que sigue la serie.</t>
-  </si>
-  <si>
-    <t>DP1-PG-20-C</t>
-  </si>
-  <si>
-    <t>Construye series de objetos, imágenes, sonidos o movimientos con base en un patrón que combine hasta tres características, magnitudes o elementos, explicando la regla del patrón.</t>
-  </si>
-  <si>
-    <t>DP1-PG-20-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-21-A</t>
-  </si>
-  <si>
-    <t>Reconoce y nombra instrumentos de percusión, viento o cuerda a partir de su forma y del sonido que emiten al explorarlos o escucharlos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-21-B</t>
-  </si>
-  <si>
-    <t>Asocia sonidos específicos con instrumentos musicales cuando escucha fragmentos de canciones o melodías conocidas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-21-C</t>
-  </si>
-  <si>
-    <t>Distingue con mayor precisión los timbres y características sonoras de distintos instrumentos, identificando similitudes y diferencias entre ellos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-21-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-22-A</t>
-  </si>
-  <si>
-    <t>Escucha diversos tipos de música y muestra interés por algunos de estos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-22-B</t>
-  </si>
-  <si>
-    <t>Muestra preferencias por algunos tipos de música.</t>
-  </si>
-  <si>
-    <t>DP1-PG-22-C</t>
-  </si>
-  <si>
-    <t>Participa en eventos sociales y culturales en los que disfruta la música que se interpreta.</t>
-  </si>
-  <si>
-    <t>DP1-PG-22-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-23-A</t>
-  </si>
-  <si>
-    <t>Disfruta combinando sonidos que produce con instrumentos musicales o materiales disponibles.</t>
-  </si>
-  <si>
-    <t>DP1-PG-23-B</t>
-  </si>
-  <si>
-    <t>Explora junto con sus compañeros diferentes cualidades del sonido (intensidad, duración, tono) usando objetos o instrumentos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-23-C</t>
-  </si>
-  <si>
-    <t>Crea y repite patrones rítmicos en grupo, utilizando instrumentos musicales o el cuerpo.</t>
-  </si>
-  <si>
-    <t>DP1-PG-23-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-24-A</t>
-  </si>
-  <si>
-    <t>Observa las diferentes creaciones artísticas de su contexto acercándose a la historia y producciones de algunos artistas locales.</t>
-  </si>
-  <si>
-    <t>DP1-PG-24-B</t>
-  </si>
-  <si>
-    <t>Aprecia las creaciones artísticas de su contexto social y de otras culturas al observarlas y conversar sobre estas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-24-C</t>
-  </si>
-  <si>
-    <t>Muestra interés por algunos detalles plásticos y visuales que observa en las distintas creaciones de artistas locales y de otras culturas a las que tiene acceso.</t>
-  </si>
-  <si>
-    <t>DP1-PG-24-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-25-A</t>
-  </si>
-  <si>
-    <t>Muestra preferencia por alguna técnica plástica y visual al explorarlas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-25-B</t>
-  </si>
-  <si>
-    <t>Utiliza diferentes técnicas plásticas y visuales para reflejar sus intereses, pensamientos, emociones y experiencias.</t>
-  </si>
-  <si>
-    <t>DP1-PG-25-C</t>
-  </si>
-  <si>
-    <t>Comparte con personas cercanas la representación de sus creaciones.</t>
-  </si>
-  <si>
-    <t>DP1-PG-25-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-26-A</t>
-  </si>
-  <si>
-    <t>Observa con atención y disfruta de presentaciones artísticas como cuentos dramatizados, obras de teatro, shows de títeres o de sombras en el contexto educativo o cultural.</t>
-  </si>
-  <si>
-    <t>DP1-PG-26-B</t>
-  </si>
-  <si>
-    <t>Expresa opiniones personales sobre lo que observa en las presentaciones, identificando personajes, situaciones y emociones representadas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-26-C</t>
-  </si>
-  <si>
-    <t>Analiza aspectos de las presentaciones artísticas a las que asiste, identificando intenciones expresivas, elementos escénicos y emociones transmitidas, relacionándolos con sus propias vivencias o ideas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-26-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-27-A</t>
-  </si>
-  <si>
-    <t>Construye con sus pares historias que luego recrea en el juego dramático.</t>
-  </si>
-  <si>
-    <t>DP1-PG-27-B</t>
-  </si>
-  <si>
-    <t>Elabora disfraces y escenarios usando material y objetos de la vida cotidiana.</t>
-  </si>
-  <si>
-    <t>DP1-PG-27-C</t>
-  </si>
-  <si>
-    <t>Establece acuerdos con sus compañeros para asignar roles en el juego dramático, respetando los gustos y preferencias de cada uno de los participantes.</t>
-  </si>
-  <si>
-    <t>DP1-PG-27-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-28-A</t>
-  </si>
-  <si>
-    <t>Presta atención a las ideas, puntos de vista, propuestas y otras situaciones de sus pares y los adultos que le rodean.</t>
-  </si>
-  <si>
-    <t>DP1-PG-28-B</t>
-  </si>
-  <si>
-    <t>Toma turnos en la comunicación para expresar sus puntos de vista y propuestas en las conversaciones que tiene con el grupo y los adultos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-28-C</t>
-  </si>
-  <si>
-    <t>Realiza comentarios en los que expresa la comprensión que hace sobre las ideas, puntos de vista y propuestas que han compartido sus pares y adultos en las conversaciones grupales.</t>
-  </si>
-  <si>
-    <t>DP1-PG-28-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-29-A</t>
-  </si>
-  <si>
-    <t>Reconoce la estructura básica de un texto narrativo (inicio, desarrollo y final) al momento de contar o recontar historias breves, e identifica si se trata de un cuento, poema, cómic u otro tipo de texto.</t>
-  </si>
-  <si>
-    <t>DP1-PG-29-B</t>
-  </si>
-  <si>
-    <t>Narra textos describiendo algunos aspectos de los personajes principales y los lugares donde ocurre la historia.</t>
-  </si>
-  <si>
-    <t>DP1-PG-29-C</t>
-  </si>
-  <si>
-    <t>Describe con mayor detalle a los personajes, el ambiente y el desenlace de los textos que ha leído o escuchado, explicando qué le gustó o no y por qué, en función de sus intereses y comprensión.</t>
-  </si>
-  <si>
-    <t>DP1-PG-29-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-30-A</t>
-  </si>
-  <si>
-    <t>Utiliza movimientos con sus manos para representar visualmente sentimientos, objetos y acciones, enfatizando el mensaje que quiere comunicar a pares y adultos en contextos específicos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-30-B</t>
-  </si>
-  <si>
-    <t>Reconoce las intenciones comunicativas de gestos y expresiones que surgen dentro de situaciones de juego o encuentros comunicativos con pares y adultos cercanos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-30-C</t>
-  </si>
-  <si>
-    <t>Responde de manera espontánea a las expresiones no verbales y gestos propuestos por pares y adultos en contextos sociales específicos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-30-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-31-A</t>
-  </si>
-  <si>
-    <t>Realiza inferencias a partir de ideas o significados que no están explícitos en los textos o en otros materiales que escucha o lee, usando pistas del contenido y su propia experiencia.</t>
-  </si>
-  <si>
-    <t>DP1-PG-31-B</t>
-  </si>
-  <si>
-    <t>Entiende el orden en que ocurren los hechos o se presentan las ideas en los textos o materiales que escucha o lee, reconociendo qué sucede primero, después y al final.</t>
-  </si>
-  <si>
-    <t>DP1-PG-31-C</t>
-  </si>
-  <si>
-    <t>Organiza con sus propias palabras lo que leyó o escuchó, explicando con claridad el orden de los hechos o ideas principales y relacionándolos con otras situaciones o experiencias.</t>
-  </si>
-  <si>
-    <t>DP1-PG-31-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-32-A</t>
-  </si>
-  <si>
-    <t>Amplía su vocabulario con nuevas palabras que escucha o lee.</t>
-  </si>
-  <si>
-    <t>DP1-PG-32-B</t>
-  </si>
-  <si>
-    <t>Utiliza las nuevas palabras y expresiones en sus conversaciones cotidianas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-32-C</t>
-  </si>
-  <si>
-    <t>Usa nuevas palabras y expresiones en la creación de textos cortos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-32-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-33-A</t>
-  </si>
-  <si>
-    <t>Escucha los sonidos que conforman una palabra para segmentar sus sílabas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-33-B</t>
-  </si>
-  <si>
-    <t>Identifica los sonidos que conforman una palabra para segmentar sus fonemas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-33-C</t>
-  </si>
-  <si>
-    <t>Manipula los fonemas de una palabra para identificar los sonidos que la conforman.</t>
-  </si>
-  <si>
-    <t>DP1-PG-33-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-34-A</t>
-  </si>
-  <si>
-    <t>Respeta la ubicación espacial y direccionalidad al escribir palabras y textos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-34-B</t>
-  </si>
-  <si>
-    <t>Escribe palabras y textos reflejando mayor precisión en sus trazos al usar diferentes superficies, tamaños de hoja y formatos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-34-C</t>
-  </si>
-  <si>
-    <t>Escribe con mayor precisión y control de sus trazos al variar el tamaño de la letra.</t>
-  </si>
-  <si>
-    <t>DP1-PG-34-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-35-A</t>
-  </si>
-  <si>
-    <t>Relaciona el sonido de las letras del alfabeto con su representación gráfica.</t>
-  </si>
-  <si>
-    <t>DP1-PG-35-B</t>
-  </si>
-  <si>
-    <t>Lee palabras y frases en diferentes textos impresos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-35-C</t>
-  </si>
-  <si>
-    <t>Realiza lectura de textos cortos y sencillos.</t>
-  </si>
-  <si>
-    <t>DP1-PG-35-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-36-A</t>
-  </si>
-  <si>
-    <t>Emplea consistentemente su lado dominante en actividades como escribir, lanzar objetos o realizar desplazamientos, mostrando mayor coordinación y control motriz.</t>
-  </si>
-  <si>
-    <t>DP1-PG-36-B</t>
-  </si>
-  <si>
-    <t>Realiza tareas que requieren uso diferenciado de ambos lados del cuerpo.</t>
-  </si>
-  <si>
-    <t>DP1-PG-36-C</t>
-  </si>
-  <si>
-    <t>Usa su lado dominante con mayor precisión en distintas actividades.</t>
-  </si>
-  <si>
-    <t>DP1-PG-36-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-37-A</t>
-  </si>
-  <si>
-    <t>Lanza, atrapa o bateas pelotas en movimiento con alguna precisión.</t>
-  </si>
-  <si>
-    <t>DP1-PG-37-B</t>
-  </si>
-  <si>
-    <t>Salta la cuerda con ambos pies o alternándolos de forma consecutiva.</t>
-  </si>
-  <si>
-    <t>DP1-PG-37-C</t>
-  </si>
-  <si>
-    <t>Se desplaza mientras patea o rebota una pelota de forma consecutiva, consiguiendo conectar con la pelota en varias ocasiones.</t>
-  </si>
-  <si>
-    <t>DP1-PG-37-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-38-A</t>
-  </si>
-  <si>
-    <t>Toma mayor consciencia de la posición de sus manos y dedos al usar materiales, utensilios y herramientas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-38-B</t>
-  </si>
-  <si>
-    <t>Recorta figuras o imágenes siguiendo su contorno de forma precisa.</t>
-  </si>
-  <si>
-    <t>DP1-PG-38-C</t>
-  </si>
-  <si>
-    <t>Realiza trazos con mayor precisión al dibujar, escribir y colorear o pintar en áreas delimitadas.</t>
-  </si>
-  <si>
-    <t>DP1-PG-38-D</t>
-  </si>
-  <si>
-    <t>DP1-PG-39-A</t>
-  </si>
-  <si>
-    <t>Practica hábitos de higiene personal, alimentación, descanso e hidratación buscando su bienestar.</t>
-  </si>
-  <si>
-    <t>DP1-PG-39-B</t>
-  </si>
-  <si>
-    <t>Reconoce que las actividades recreativas, lúdicas o físicas contribuyen a su bienestar.</t>
-  </si>
-  <si>
-    <t>DP1-PG-39-C</t>
-  </si>
-  <si>
-    <t>Reutiliza materiales, envases plásticos, entre otros y pone en práctica acciones para la preservación de los recursos naturales en su comunidad.</t>
-  </si>
-  <si>
-    <t>DP1-PG-39-D</t>
+    <t>DP1-P4-01-A</t>
+  </si>
+  <si>
+    <t>Describe sus propias características físicas y habilidades, lo cual evidencia mayor conocimiento de sí mismo.</t>
+  </si>
+  <si>
+    <t>DP1-P4-01-B</t>
+  </si>
+  <si>
+    <t>Expresa de manera oral sus gustos, preferencias, intereses y cosas que no son de su agrado, muestra mayor determinación y confianza en sí mismo.</t>
+  </si>
+  <si>
+    <t>DP1-P4-01-C</t>
+  </si>
+  <si>
+    <t>Busca relacionarse con pares que compartan sus intereses en actividades, juguetes y alimentos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-01-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-02-A</t>
+  </si>
+  <si>
+    <t>Representa diferentes roles sociales y situaciones en juegos y actividades en los que pone en práctica su independencia.</t>
+  </si>
+  <si>
+    <t>DP1-P4-02-B</t>
+  </si>
+  <si>
+    <t>Organiza con pares juegos y actividades en los que se evidencia su autonomía al tomar decisiones y recrear las situaciones sin la intervención los adultos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-02-C</t>
+  </si>
+  <si>
+    <t>Resuelve situaciones o problemas que se presentan en los juegos y el desarrollo de actividades de manera autónoma.</t>
+  </si>
+  <si>
+    <t>DP1-P4-02-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-03-A</t>
+  </si>
+  <si>
+    <t>Muestra seguridad al conversar o compartir espacios y actividades con pares y adultos en diferentes contextos en compañía de familiares y adultos cuidadores.</t>
+  </si>
+  <si>
+    <t>DP1-P4-03-B</t>
+  </si>
+  <si>
+    <t>Inicia conversaciones espontáneamente con pares y adultos sobre actividades y acontecimientos cotidianos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-03-C</t>
+  </si>
+  <si>
+    <t>Organiza juegos de roles sociales con sus pares sobre actividades y experiencias observadas en su entorno.</t>
+  </si>
+  <si>
+    <t>DP1-P4-03-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-04-A</t>
+  </si>
+  <si>
+    <t>Utiliza estrategias para calmar y regular sus emociones, como respirar o buscar el apoyo de un adulto para tranquilizarse.</t>
+  </si>
+  <si>
+    <t>DP1-P4-04-B</t>
+  </si>
+  <si>
+    <t>Muestra mayor interés en los sentimientos y necesidades de los demás, al comprender diferentes perspectivas y puntos de vista.</t>
+  </si>
+  <si>
+    <t>DP1-P4-04-C</t>
+  </si>
+  <si>
+    <t>Muestra empatía por pares y adultos observando sus reacciones y ofreciéndoles consuelo cuando están tristes o molestos, por medio de contacto físico o verbal.</t>
+  </si>
+  <si>
+    <t>DP1-P4-04-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-05-A</t>
+  </si>
+  <si>
+    <t>Participa en juegos y actividades grupales, con apoyo ocasional de un adulto, para compartir y organizar los espacios, juguetes, materiales y celebraciones.</t>
+  </si>
+  <si>
+    <t>DP1-P4-05-B</t>
+  </si>
+  <si>
+    <t>Planifica y organiza actividades grupales y de juego, con sus pares, estableciendo algunos acuerdos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-05-C</t>
+  </si>
+  <si>
+    <t>Participa activamente en juegos colaborativos, asumiendo normas de convivencia.</t>
+  </si>
+  <si>
+    <t>DP1-P4-05-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-06-A</t>
+  </si>
+  <si>
+    <t>Busca la orientación del adulto para resolver conflictos, los reconoce como figuras de autoridad y mediadores de las situaciones.</t>
+  </si>
+  <si>
+    <t>DP1-P4-06-B</t>
+  </si>
+  <si>
+    <t>Plantea propuestas para resolver conflictos con sus pares y solicita la aprobación y el apoyo del adulto.</t>
+  </si>
+  <si>
+    <t>DP1-P4-06-C</t>
+  </si>
+  <si>
+    <t>Pone en práctica los acuerdos establecidos con sus pares para resolver los conflictos cada vez con menos intermediación de los adultos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-06-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-07-A</t>
+  </si>
+  <si>
+    <t>Ejerce diferentes acciones sobre objetos y elementos naturales del entorno, observando cambios y reacciones.</t>
+  </si>
+  <si>
+    <t>DP1-P4-07-B</t>
+  </si>
+  <si>
+    <t>Identifica cambios y reacciones que suceden al ejercer algunas acciones sobre objetos y elementos naturales del entorno.</t>
+  </si>
+  <si>
+    <t>DP1-P4-07-C</t>
+  </si>
+  <si>
+    <t>Explica con sus propias palabras el cambio observado al realizar una acción sobre elementos naturales u objetos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-07-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-08-A</t>
+  </si>
+  <si>
+    <t>Formula hipótesis sobre los cambios que observa en la naturaleza y sobre los acontecimientos relacionados con los fenómenos físico-naturales y el funcionamiento de su cuerpo.</t>
+  </si>
+  <si>
+    <t>DP1-P4-08-B</t>
+  </si>
+  <si>
+    <t>Comprueba hipótesis mediante la experimentación, haciendo la misma secuencia de pasos una y otra vez.</t>
+  </si>
+  <si>
+    <t>DP1-P4-08-C</t>
+  </si>
+  <si>
+    <t>Comprende algunas propiedades y características de los objetos y elementos naturales estableciendo conclusiones a partir de la observación y experimentación.</t>
+  </si>
+  <si>
+    <t>DP1-P4-08-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-09-A</t>
+  </si>
+  <si>
+    <t>Muestra interés por conocer más sobre los objetos, animales, fenómenos físicos, naturales y elementos de la naturaleza mediante sus intervenciones, preguntas, propuestas e indagaciones.</t>
+  </si>
+  <si>
+    <t>DP1-P4-09-B</t>
+  </si>
+  <si>
+    <t>Busca obtener respuestas y explicaciones a sus interrogantes al preguntar a los adultos, pares o consultar recursos como libros y videos cortos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-09-C</t>
+  </si>
+  <si>
+    <t>Explica de manera verbal o por medio de ilustraciones el porqué de los acontecimientos que observa.</t>
+  </si>
+  <si>
+    <t>DP1-P4-09-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-10-A</t>
+  </si>
+  <si>
+    <t>Comprende la relación entre sus acciones y las reacciones que desencadenan.</t>
+  </si>
+  <si>
+    <t>DP1-P4-10-B</t>
+  </si>
+  <si>
+    <t>Anticipa las consecuencias al realizar una acción de manera repetida sobre diferentes objetos o materiales.</t>
+  </si>
+  <si>
+    <t>DP1-P4-10-C</t>
+  </si>
+  <si>
+    <t>Explica con sus propias palabras la reacción provocada por las acciones que realiza.</t>
+  </si>
+  <si>
+    <t>DP1-P4-10-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-11-A</t>
+  </si>
+  <si>
+    <t>Expresa interés en el funcionamiento de los objetos y aparatos tecnológicos, explorándolos intuitivamente, presionando botones, deslizando pantallas táctiles, entre otras acciones.</t>
+  </si>
+  <si>
+    <t>DP1-P4-11-B</t>
+  </si>
+  <si>
+    <t>Identifica la función de objetos5 cotidianos y aparatos tecnológicos, y los utiliza de manera creativa, no convencional, en juegos o situaciones cotidianas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-11-C</t>
+  </si>
+  <si>
+    <t>Ofrece explicaciones sobre el funcionamiento de los objetos y aparatos a partir de la información que obtiene de los adultos u otros recursos, como libros o videos cortos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-11-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-12-A</t>
+  </si>
+  <si>
+    <t>Analiza los problemas que se le presentan, identificando algunas variables y puntos clave para encontrar una solución.</t>
+  </si>
+  <si>
+    <t>DP1-P4-12-B</t>
+  </si>
+  <si>
+    <t>Planifica acciones y estrategias para resolver problemas que se le presentan.</t>
+  </si>
+  <si>
+    <t>DP1-P4-12-C</t>
+  </si>
+  <si>
+    <t>Ejecuta estrategias planificadas, llevando a cabo acciones específicas para resolver un problema.</t>
+  </si>
+  <si>
+    <t>DP1-P4-12-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-13-A</t>
+  </si>
+  <si>
+    <t>Comprende la secuencia para preparar recetas, construir estructuras y aparatos que requieren pocos pasos para su realización.</t>
+  </si>
+  <si>
+    <t>DP1-P4-13-B</t>
+  </si>
+  <si>
+    <t>Sigue paso a paso las indicaciones del adulto en la preparación de recetas o en la construcción de estructuras y aparatos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-13-C</t>
+  </si>
+  <si>
+    <t>Completa tareas, de manera más independiente, que requieren seguir instrucciones simples de múltiples pasos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-13-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-14-A</t>
+  </si>
+  <si>
+    <t>Ubica objetos de su entorno tomando como punto de referencia otro objeto.</t>
+  </si>
+  <si>
+    <t>DP1-P4-14-B</t>
+  </si>
+  <si>
+    <t>Reconoce la ubicación de la mayoría de los objetos de su entorno, utilizando puntos de referencia.</t>
+  </si>
+  <si>
+    <t>DP1-P4-14-C</t>
+  </si>
+  <si>
+    <t>Expresa la posición de objetos de su entorno utilizando términos como: arriba de, abajo de, encima de, debajo de, lejos de, cerca de, adentro de, afuera de, entre otros.</t>
+  </si>
+  <si>
+    <t>DP1-P4-14-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-15-A</t>
+  </si>
+  <si>
+    <t>Identifica similitudes y diferencias entre objetos, imágenes u otros elementos de su entorno con base en una o dos características, expresando las similitudes y diferencias encontradas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-15-B</t>
+  </si>
+  <si>
+    <t>Elige una o dos características para armar colecciones de objetos, identificando y agrupando aquellos que cumplen con dichas características, en actividades de la vida cotidiana.</t>
+  </si>
+  <si>
+    <t>DP1-P4-15-C</t>
+  </si>
+  <si>
+    <t>Identifica los elementos que no corresponden dentro de una colección o serie, reconociendo la característica o regla que la organiza y comparando similitudes y diferencias entre los objetos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-15-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-16-A</t>
+  </si>
+  <si>
+    <t>Comprende el significado de algunas expresiones relacionadas con el tiempo: día, noche, mañana, tarde, antes, después, más tarde, otro día o en la mañana.</t>
+  </si>
+  <si>
+    <t>DP1-P4-16-B</t>
+  </si>
+  <si>
+    <t>Explica las actividades que realiza en su rutina utilizando términos como: ayer, hoy o mañana, algunos aún con poca precisión.</t>
+  </si>
+  <si>
+    <t>DP1-P4-16-C</t>
+  </si>
+  <si>
+    <t>Secuencia tres actividades de la rutina o imágenes atendiendo a un orden cronológico.</t>
+  </si>
+  <si>
+    <t>DP1-P4-16-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-17-A</t>
+  </si>
+  <si>
+    <t>Usa estrategias para comparar la cantidad de objetos de dos conjuntos, como la correspondencia uno a uno, o al apilarlos de manera vertical u horizontal.</t>
+  </si>
+  <si>
+    <t>DP1-P4-17-B</t>
+  </si>
+  <si>
+    <t>Compara la cantidad de elementos de dos conjuntos, identificando si uno de ellos tiene más o menos objetos, o si tienen la misma cantidad.</t>
+  </si>
+  <si>
+    <t>DP1-P4-17-C</t>
+  </si>
+  <si>
+    <t>Expresa las comparaciones de cantidad realizadas utilizando términos como: más que, menos que o igual que.</t>
+  </si>
+  <si>
+    <t>DP1-P4-17-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-18-A</t>
+  </si>
+  <si>
+    <t>Compara directamente dos objetos, expresando la relación encontrada con términos como: más que, menos que o igual que.</t>
+  </si>
+  <si>
+    <t>DP1-P4-18-B</t>
+  </si>
+  <si>
+    <t>Explora instrumentos de medición convencionales, identificando para qué sirven algunos de ellos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-18-C</t>
+  </si>
+  <si>
+    <t>Mide y compara la longitud de dos objetos que no pueden colocarse uno al lado del otro, utilizando partes de su cuerpo, como sus manos o pies.</t>
+  </si>
+  <si>
+    <t>DP1-P4-18-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-19-A</t>
+  </si>
+  <si>
+    <t>Identifica líneas, figuras y cuerpos geométricos presentes en el entorno, nombrando algunos de ellos y clasificándolos según su forma de triángulo, forma de cuadrado, forma de círculo, forma de rectángulo, línea abierta, línea cerrada.</t>
+  </si>
+  <si>
+    <t>DP1-P4-19-B</t>
+  </si>
+  <si>
+    <t>Empareja figuras o imágenes teniendo en cuenta una o dos características, como forma, color o función.</t>
+  </si>
+  <si>
+    <t>DP1-P4-19-C</t>
+  </si>
+  <si>
+    <t>Arma rompecabezas con piezas grandes por medio de ensayo y error, y construye diferentes estructuras utilizando material concreto, como bloques o figuras.</t>
+  </si>
+  <si>
+    <t>DP1-P4-19-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-20-A</t>
+  </si>
+  <si>
+    <t>Compone conjuntos de tres a cinco objetos uniendo dos grupos más pequeños, o descompone un conjunto en dos grupos más pequeños.</t>
+  </si>
+  <si>
+    <t>DP1-P4-20-B</t>
+  </si>
+  <si>
+    <t>Agrupa objetos de dos conjuntos diferentes, utilizando el conteo de uno en uno para saber cuántos elementos hay, con totales de hasta diez.</t>
+  </si>
+  <si>
+    <t>DP1-P4-20-C</t>
+  </si>
+  <si>
+    <t>Separa un conjunto de hasta diez objetos en dos grupos distintos, utilizando el conteo de uno en uno para determinar cuántos elementos quedan en cada grupo.</t>
+  </si>
+  <si>
+    <t>DP1-P4-20-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-21-A</t>
+  </si>
+  <si>
+    <t>Cuenta los objetos de un conjunto de hasta diez elementos, asociando cada uno con un número mediante subconteo o sobreconteo, logrando vincular cada elemento finalmente con un único número y relacionar el número final con el total de los objetos del conjunto.</t>
+  </si>
+  <si>
+    <t>DP1-P4-21-B</t>
+  </si>
+  <si>
+    <t>Asocia el nombre de los números con su símbolo, imitando el trazo de algunos números entre el uno y el diez, aunque con poca precisión.</t>
+  </si>
+  <si>
+    <t>DP1-P4-21-C</t>
+  </si>
+  <si>
+    <t>Reconoce la función del dinero, utilizando monedas y billetes en actividades cotidianas o durante el juego de roles, identificando similitudes y diferencias en sus características físicas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-21-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-22-A</t>
+  </si>
+  <si>
+    <t>Forma series de objetos o imágenes, con un patrón definido por una o dos características.</t>
+  </si>
+  <si>
+    <t>DP1-P4-22-B</t>
+  </si>
+  <si>
+    <t>Ordena objetos con base en una o dos magnitudes, como tamaño, longitud o peso, de forma creciente o decreciente.</t>
+  </si>
+  <si>
+    <t>DP1-P4-22-C</t>
+  </si>
+  <si>
+    <t>Continúa series de objetos o imágenes siguiendo un patrón definido por una característica, identificando el elemento que sigue después del último colocado y respetando la regla del patrón.</t>
+  </si>
+  <si>
+    <t>DP1-P4-22-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-23-A</t>
+  </si>
+  <si>
+    <t>Identifica los sonidos que escucha, aun cuando no ve el elemento o instrumento que lo está produciendo.</t>
+  </si>
+  <si>
+    <t>DP1-P4-23-B</t>
+  </si>
+  <si>
+    <t>Discrimina los sonidos que escucha identificando en qué lugares o situaciones están presente, o qué animales, personajes u objetos los producen.</t>
+  </si>
+  <si>
+    <t>DP1-P4-23-C</t>
+  </si>
+  <si>
+    <t>Asocia lugares, situaciones, animales, objetos y personas con los sonidos que escucha en los diferentes paisajes sonoros.</t>
+  </si>
+  <si>
+    <t>DP1-P4-23-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-24-A</t>
+  </si>
+  <si>
+    <t>Intenta llevar el pulso de las canciones con alguna parte de su cuerpo o elemento cotidiano.</t>
+  </si>
+  <si>
+    <t>DP1-P4-24-B</t>
+  </si>
+  <si>
+    <t>Lleva el pulso con sus manos, pies o algún instrumento de percusión de las canciones que le cantan o le gustan.</t>
+  </si>
+  <si>
+    <t>DP1-P4-24-C</t>
+  </si>
+  <si>
+    <t>Canta y baila llevando el ritmo y la melodía de las canciones que le gustan.</t>
+  </si>
+  <si>
+    <t>DP1-P4-24-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-25-A</t>
+  </si>
+  <si>
+    <t>Identifica sonidos graves y agudos, fuertes y suaves en los juegos rítmicos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-25-B</t>
+  </si>
+  <si>
+    <t>Aprecia el silencio como una pausa que se hace en los juegos rítmicos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-25-C</t>
+  </si>
+  <si>
+    <t>Asocia expresiones faciales e imágenes con sonidos fuertes suaves, agudos y graves.</t>
+  </si>
+  <si>
+    <t>DP1-P4-25-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-26-A</t>
+  </si>
+  <si>
+    <t>Expresa su agrado o desagrado al observar sus propias expresiones plásticas y las de los demás.</t>
+  </si>
+  <si>
+    <t>DP1-P4-26-B</t>
+  </si>
+  <si>
+    <t>Observa pinturas, esculturas, obras arquitectónicas y patrimonio cultural.</t>
+  </si>
+  <si>
+    <t>DP1-P4-26-C</t>
+  </si>
+  <si>
+    <t>Expresa su agrado o desagrado al apreciar pinturas, esculturas, obras arquitectónicas y patrimonio cultural como artesanías o danzas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-26-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-27-A</t>
+  </si>
+  <si>
+    <t>Observa las hojas, flores, árboles, nubes, entre otros elementos de la naturaleza.</t>
+  </si>
+  <si>
+    <t>DP1-P4-27-B</t>
+  </si>
+  <si>
+    <t>Experimenta con diferentes materiales para representar los elementos de la naturaleza y el entorno a través de diferentes expresiones plásticas y visuales como el dibujo, modelado o pintura.</t>
+  </si>
+  <si>
+    <t>DP1-P4-27-C</t>
+  </si>
+  <si>
+    <t>Realiza creaciones plásticas y visuales en las que busca representar detalles observados en la naturaleza y su entorno.</t>
+  </si>
+  <si>
+    <t>DP1-P4-27-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-28-A</t>
+  </si>
+  <si>
+    <t>Se disfraza de su personaje preferido, imita su voz, posturas y acciones.</t>
+  </si>
+  <si>
+    <t>DP1-P4-28-B</t>
+  </si>
+  <si>
+    <t>Recrea historias con sus pares en las que crean escenarios y mundos imaginarios.</t>
+  </si>
+  <si>
+    <t>DP1-P4-28-C</t>
+  </si>
+  <si>
+    <t>Crea historias en las que su personaje preferido es el protagonista.</t>
+  </si>
+  <si>
+    <t>DP1-P4-28-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-29-A</t>
+  </si>
+  <si>
+    <t>Asume un rol social en el juego simbólico e improvisa la historia de su personaje.</t>
+  </si>
+  <si>
+    <t>DP1-P4-29-B</t>
+  </si>
+  <si>
+    <t>Crea escenarios y disfraces utilizando su imaginación o los materiales que tiene a su alcance.</t>
+  </si>
+  <si>
+    <t>DP1-P4-29-C</t>
+  </si>
+  <si>
+    <t>Vincula a su juego a otros niños con quienes improvisan situaciones y escenarios.</t>
+  </si>
+  <si>
+    <t>DP1-P4-29-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-30-A</t>
+  </si>
+  <si>
+    <t>Muestra interés al jugar con la repetición de sonidos vocálicos y consonánticos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-30-B</t>
+  </si>
+  <si>
+    <t>Juega al repetir sonidos vocálicos y consonánticos, participando en actividades más estructuradas como rondas, canciones, rimas y trabalenguas en los que recuerda y emite sonidos onomatopéyicos para imitar otros sonidos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-30-C</t>
+  </si>
+  <si>
+    <t>Cambia la estructura de las palabras al familiarizarse con el uso de reglas gramaticales más complejas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-30-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-31-A</t>
+  </si>
+  <si>
+    <t>Demuestra que usa palabras para describir aspectos que resaltan o llaman su atención de personas, animales y objetos a su alrededor.</t>
+  </si>
+  <si>
+    <t>DP1-P4-31-B</t>
+  </si>
+  <si>
+    <t>Describe las personas y objetos a su alrededor con palabras que le son familiares, e incorpora nuevas para enfatizar en sus características.</t>
+  </si>
+  <si>
+    <t>DP1-P4-31-C</t>
+  </si>
+  <si>
+    <t>Expresa descripciones con una variedad de palabras para nombrar distintas características de lo que observa y emplea combinaciones y orden de palabras más complejas para brindar explicaciones más detalladas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-31-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-32-A</t>
+  </si>
+  <si>
+    <t>Entiende la mayoría de los gestos icónicos y señas que hacen adultos y pares para comunicarle algo.</t>
+  </si>
+  <si>
+    <t>DP1-P4-32-B</t>
+  </si>
+  <si>
+    <t>Interpreta la mayoría de los gestos icónicos y señas cuando le comunican algo sin muchos movimientos, particularmente miradas, gestos faciales y la distancia que mantienen otros al hablarle.</t>
+  </si>
+  <si>
+    <t>DP1-P4-32-C</t>
+  </si>
+  <si>
+    <t>Comprende el uso de determinados gestos y movimientos en contextos sociales.</t>
+  </si>
+  <si>
+    <t>DP1-P4-32-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-33-A</t>
+  </si>
+  <si>
+    <t>Muestra interés en ciertas expresiones no verbales que hacen los adultos o pares.</t>
+  </si>
+  <si>
+    <t>DP1-P4-33-B</t>
+  </si>
+  <si>
+    <t>Imita expresiones corporales y gestos faciales de adultos y pares con los que participa en situaciones en las que se cumplen ciertas convencionalidades que median las interacciones y forma de comunicarse.</t>
+  </si>
+  <si>
+    <t>DP1-P4-33-C</t>
+  </si>
+  <si>
+    <t>Apropia gestos y expresiones que ha observado en otros, utilizándolos para darse a entender según los diferentes contextos en los que participa.</t>
+  </si>
+  <si>
+    <t>DP1-P4-33-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-34-A</t>
+  </si>
+  <si>
+    <t>Sigue con la mirada o con su dedo lo que le lee el adulto, esto le permite identificar la direccionalidad de la lectura.</t>
+  </si>
+  <si>
+    <t>DP1-P4-34-B</t>
+  </si>
+  <si>
+    <t>Participa en la lectura de cuentos haciendo predicciones a partir de las imágenes de este o cambiando su final.</t>
+  </si>
+  <si>
+    <t>DP1-P4-34-C</t>
+  </si>
+  <si>
+    <t>Hace predicciones de los cuentos o historias a partir del título que escucha leer.</t>
+  </si>
+  <si>
+    <t>DP1-P4-34-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-35-A</t>
+  </si>
+  <si>
+    <t>Usa palabras que ha escuchado en diferentes situaciones para ampliar sus conversaciones.</t>
+  </si>
+  <si>
+    <t>DP1-P4-35-B</t>
+  </si>
+  <si>
+    <t>Incorpora términos menos habituales para expresar cómo se siente o qué sucede.</t>
+  </si>
+  <si>
+    <t>DP1-P4-35-C</t>
+  </si>
+  <si>
+    <t>Diferencia palabras que expresan ideas similares, eligiendo la que mejor se ajusta al contexto.</t>
+  </si>
+  <si>
+    <t>DP1-P4-35-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-36-A</t>
+  </si>
+  <si>
+    <t>Participa en juegos orales donde reconoce las palabras que forman frases y oraciones sencillas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-36-B</t>
+  </si>
+  <si>
+    <t>Identifica palabras que riman en canciones, juegos, poemas y cuentos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-36-C</t>
+  </si>
+  <si>
+    <t>Separa palabras familiares en sílabas de forma oral utilizando apoyos rítmicos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-36-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-37-A</t>
+  </si>
+  <si>
+    <t>Percibe el sonido de las vocales que encuentra en su nombre y palabras que le son familiares.</t>
+  </si>
+  <si>
+    <t>DP1-P4-37-B</t>
+  </si>
+  <si>
+    <t>Identifica el sonido de las vocales que encuentra en su nombre y palabras que le son familiares.</t>
+  </si>
+  <si>
+    <t>DP1-P4-37-C</t>
+  </si>
+  <si>
+    <t>Intenta escribir su nombre utilizando sus propias grafías, en las que se reconocen trazos similares a las vocales.</t>
+  </si>
+  <si>
+    <t>DP1-P4-37-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-38-A</t>
+  </si>
+  <si>
+    <t>Sigue instrucciones relacionadas con el movimiento y desplazamiento de acuerdo con su posición en el espacio.</t>
+  </si>
+  <si>
+    <t>DP1-P4-38-B</t>
+  </si>
+  <si>
+    <t>Amplían la conciencia espacial y corporal al orientarse en su entorno, moverse por los espacios evitando tropezar.</t>
+  </si>
+  <si>
+    <t>DP1-P4-38-C</t>
+  </si>
+  <si>
+    <t>Reconoce, recuerda y se orienta en relación a lugares que frecuenta en compañía de los adultos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-38-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-39-A</t>
+  </si>
+  <si>
+    <t>Salta con ambos pies hacia diferentes direcciones y supera obstáculos que encuentra en el desplazamiento.</t>
+  </si>
+  <si>
+    <t>DP1-P4-39-B</t>
+  </si>
+  <si>
+    <t>Transporta objetos de un lado al otro, corriendo a diferentes velocidades y siguiendo líneas curvas y zigzag.</t>
+  </si>
+  <si>
+    <t>DP1-P4-39-C</t>
+  </si>
+  <si>
+    <t>Ajusta la postura corporal al desplazarse, saltar y atrapar objetos con ambas manos.</t>
+  </si>
+  <si>
+    <t>DP1-P4-39-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-40-A</t>
+  </si>
+  <si>
+    <t>Colabora en acciones de la vida cotidiana en las que controla los movimientos de sus manos al usar objetos, utensilios y herramientas.</t>
+  </si>
+  <si>
+    <t>DP1-P4-40-B</t>
+  </si>
+  <si>
+    <t>Construye diferentes estructuras utilizando bloques u otros materiales que se pueden ensartar, encajar o enroscar.</t>
+  </si>
+  <si>
+    <t>DP1-P4-40-C</t>
+  </si>
+  <si>
+    <t>Controla los movimientos de manos y dedos para realizar acciones que requieren mayor precisión, como colorear, hacer dibujos o utilizar la tijera.</t>
+  </si>
+  <si>
+    <t>DP1-P4-40-D</t>
+  </si>
+  <si>
+    <t>DP1-P4-41-A</t>
+  </si>
+  <si>
+    <t>Consume alimentos saludables o bebe agua al sentir necesidad de ellos, también realiza acciones de higiene personal con mayor conciencia y autonomía.</t>
+  </si>
+  <si>
+    <t>DP1-P4-41-B</t>
+  </si>
+  <si>
+    <t>Disfruta del juego en espacios abiertos y en contacto con la naturaleza e identifica cuando se siente cansado y busca un tiempo y espacio para su descanso.</t>
+  </si>
+  <si>
+    <t>DP1-P4-41-C</t>
+  </si>
+  <si>
+    <t>Comienza a tener mayor conciencia del cuidado y limpieza de su entorno al botar la basura en su lugar o mantener ordenados sus juguetes.</t>
+  </si>
+  <si>
+    <t>DP1-P4-41-D</t>
   </si>
 </sst>
 </file>
@@ -1491,7 +1500,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AO27"/>
+  <dimension ref="A1:AQ17"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="15.140625" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="3" max="3" width="28.140625" customWidth="true" style="0"/>
@@ -1533,138 +1542,146 @@
     <col min="39" max="39" width="28.140625" customWidth="true" style="0"/>
     <col min="40" max="40" width="28.140625" customWidth="true" style="0"/>
     <col min="41" max="41" width="28.140625" customWidth="true" style="0"/>
+    <col min="42" max="42" width="28.28515625" customWidth="true" style="0"/>
+    <col min="43" max="43" width="28.28515625" customWidth="true" style="0"/>
     <col min="1" max="1" width="12" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="43" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="42" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" customHeight="1" ht="149.25">
+    <row r="1" spans="1:43" customHeight="1" ht="149.25">
       <c r="A1" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:41" customHeight="1" ht="60">
+    <row r="2" spans="1:43" customHeight="1" ht="60">
       <c r="A2" s="5">
-        <v>10782664</v>
+        <v>11116071</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>1</v>
@@ -1786,13 +1803,19 @@
       <c r="AO2" s="10" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:41" customHeight="1" ht="60">
+      <c r="AP2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ2" s="10" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:43" customHeight="1" ht="60">
       <c r="A3" s="7">
-        <v>10557767</v>
+        <v>11196827</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>0</v>
@@ -1911,13 +1934,19 @@
       <c r="AO3" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:41" customHeight="1" ht="60">
+      <c r="AP3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ3" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:43" customHeight="1" ht="60">
       <c r="A4" s="5">
-        <v>11096587</v>
+        <v>11086137</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>0</v>
@@ -2036,13 +2065,19 @@
       <c r="AO4" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:41" customHeight="1" ht="60">
+      <c r="AP4" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" customHeight="1" ht="60">
       <c r="A5" s="7">
-        <v>10662107</v>
+        <v>11184491</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C5" s="11" t="s">
         <v>0</v>
@@ -2161,13 +2196,19 @@
       <c r="AO5" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:41" customHeight="1" ht="60">
+      <c r="AP5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ5" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:43" customHeight="1" ht="60">
       <c r="A6" s="5">
-        <v>10662114</v>
+        <v>11196324</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>0</v>
@@ -2286,13 +2327,19 @@
       <c r="AO6" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:41" customHeight="1" ht="60">
+      <c r="AP6" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:43" customHeight="1" ht="60">
       <c r="A7" s="7">
-        <v>10730806</v>
+        <v>11208124</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>0</v>
@@ -2411,13 +2458,19 @@
       <c r="AO7" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:41" customHeight="1" ht="60">
+      <c r="AP7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:43" customHeight="1" ht="60">
       <c r="A8" s="5">
-        <v>10744414</v>
+        <v>11109520</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>0</v>
@@ -2536,13 +2589,19 @@
       <c r="AO8" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:41" customHeight="1" ht="60">
+      <c r="AP8" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:43" customHeight="1" ht="60">
       <c r="A9" s="7">
-        <v>10891577</v>
+        <v>11181959</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>0</v>
@@ -2661,13 +2720,19 @@
       <c r="AO9" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:41" customHeight="1" ht="60">
+      <c r="AP9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:43" customHeight="1" ht="60">
       <c r="A10" s="5">
-        <v>10740232</v>
+        <v>11116067</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>0</v>
@@ -2786,13 +2851,19 @@
       <c r="AO10" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:41" customHeight="1" ht="60">
+      <c r="AP10" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:43" customHeight="1" ht="60">
       <c r="A11" s="7">
-        <v>11039874</v>
+        <v>11116053</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>0</v>
@@ -2911,13 +2982,19 @@
       <c r="AO11" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:41" customHeight="1" ht="60">
+      <c r="AP11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:43" customHeight="1" ht="60">
       <c r="A12" s="5">
-        <v>10744557</v>
+        <v>11116069</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>0</v>
@@ -3036,13 +3113,19 @@
       <c r="AO12" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:41" customHeight="1" ht="60">
+      <c r="AP12" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:43" customHeight="1" ht="60">
       <c r="A13" s="7">
-        <v>11182811</v>
+        <v>10975640</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>0</v>
@@ -3161,13 +3244,19 @@
       <c r="AO13" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:41" customHeight="1" ht="60">
+      <c r="AP13" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:43" customHeight="1" ht="60">
       <c r="A14" s="5">
-        <v>10762549</v>
+        <v>11197046</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>0</v>
@@ -3286,14 +3375,16 @@
       <c r="AO14" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:41" customHeight="1" ht="60">
-      <c r="A15" s="7">
-        <v>11027602</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>55</v>
-      </c>
+      <c r="AP14" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:43" customHeight="1" ht="60">
+      <c r="A15" s="7"/>
+      <c r="B15" s="8"/>
       <c r="C15" s="11" t="s">
         <v>0</v>
       </c>
@@ -3411,14 +3502,16 @@
       <c r="AO15" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:41" customHeight="1" ht="60">
-      <c r="A16" s="5">
-        <v>10878662</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>56</v>
-      </c>
+      <c r="AP15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:43" customHeight="1" ht="60">
+      <c r="A16" s="5"/>
+      <c r="B16" s="9"/>
       <c r="C16" s="11" t="s">
         <v>0</v>
       </c>
@@ -3536,14 +3629,16 @@
       <c r="AO16" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:41" customHeight="1" ht="60">
-      <c r="A17" s="7">
-        <v>10803817</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>57</v>
-      </c>
+      <c r="AP16" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="12" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:43" customHeight="1" ht="60">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="11" t="s">
         <v>0</v>
       </c>
@@ -3661,1473 +3756,227 @@
       <c r="AO17" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:41" customHeight="1" ht="60">
-      <c r="A18" s="5">
-        <v>10751410</v>
-      </c>
-      <c r="B18" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN18" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO18" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:41" customHeight="1" ht="60">
-      <c r="A19" s="7">
-        <v>10869391</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:41" customHeight="1" ht="60">
-      <c r="A20" s="5">
-        <v>10541138</v>
-      </c>
-      <c r="B20" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:41" customHeight="1" ht="60">
-      <c r="A21" s="7">
-        <v>10554374</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:41" customHeight="1" ht="60">
-      <c r="A22" s="5">
-        <v>10755757</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:41" customHeight="1" ht="60">
-      <c r="A23" s="7">
-        <v>10755771</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:41" customHeight="1" ht="60">
-      <c r="A24" s="5">
-        <v>11031046</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:41" customHeight="1" ht="60">
-      <c r="A25" s="7">
-        <v>11031060</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:41" customHeight="1" ht="60">
-      <c r="A26" s="5">
-        <v>10937304</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="12" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:41" customHeight="1" ht="60">
-      <c r="A27" s="7">
-        <v>10937419</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="E27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="F27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="G27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="H27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="J27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="K27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="L27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="M27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="N27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Q27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="R27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="S27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="T27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="U27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="V27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="W27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="X27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AH27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AI27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AJ27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AK27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AL27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AM27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="12" t="s">
+      <c r="AP17" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="12" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
-  <conditionalFormatting sqref="C2:C27">
+  <conditionalFormatting sqref="C2:C17">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D27">
+  <conditionalFormatting sqref="D2:D17">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E27">
+  <conditionalFormatting sqref="E2:E17">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F27">
+  <conditionalFormatting sqref="F2:F17">
     <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G27">
+  <conditionalFormatting sqref="G2:G17">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H27">
+  <conditionalFormatting sqref="H2:H17">
     <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I27">
+  <conditionalFormatting sqref="I2:I17">
     <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J27">
+  <conditionalFormatting sqref="J2:J17">
     <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K27">
+  <conditionalFormatting sqref="K2:K17">
     <cfRule type="cellIs" dxfId="0" priority="9" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L27">
+  <conditionalFormatting sqref="L2:L17">
     <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M27">
+  <conditionalFormatting sqref="M2:M17">
     <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N27">
+  <conditionalFormatting sqref="N2:N17">
     <cfRule type="cellIs" dxfId="0" priority="12" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O27">
+  <conditionalFormatting sqref="O2:O17">
     <cfRule type="cellIs" dxfId="0" priority="13" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P27">
+  <conditionalFormatting sqref="P2:P17">
     <cfRule type="cellIs" dxfId="0" priority="14" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q27">
+  <conditionalFormatting sqref="Q2:Q17">
     <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R27">
+  <conditionalFormatting sqref="R2:R17">
     <cfRule type="cellIs" dxfId="0" priority="16" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S27">
+  <conditionalFormatting sqref="S2:S17">
     <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T27">
+  <conditionalFormatting sqref="T2:T17">
     <cfRule type="cellIs" dxfId="0" priority="18" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U27">
+  <conditionalFormatting sqref="U2:U17">
     <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V27">
+  <conditionalFormatting sqref="V2:V17">
     <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W27">
+  <conditionalFormatting sqref="W2:W17">
     <cfRule type="cellIs" dxfId="0" priority="21" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X2:X27">
+  <conditionalFormatting sqref="X2:X17">
     <cfRule type="cellIs" dxfId="0" priority="22" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y2:Y27">
+  <conditionalFormatting sqref="Y2:Y17">
     <cfRule type="cellIs" dxfId="0" priority="23" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:Z27">
+  <conditionalFormatting sqref="Z2:Z17">
     <cfRule type="cellIs" dxfId="0" priority="24" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA27">
+  <conditionalFormatting sqref="AA2:AA17">
     <cfRule type="cellIs" dxfId="0" priority="25" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AB27">
+  <conditionalFormatting sqref="AB2:AB17">
     <cfRule type="cellIs" dxfId="0" priority="26" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC2:AC27">
+  <conditionalFormatting sqref="AC2:AC17">
     <cfRule type="cellIs" dxfId="0" priority="27" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AD27">
+  <conditionalFormatting sqref="AD2:AD17">
     <cfRule type="cellIs" dxfId="0" priority="28" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE2:AE27">
+  <conditionalFormatting sqref="AE2:AE17">
     <cfRule type="cellIs" dxfId="0" priority="29" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AF27">
+  <conditionalFormatting sqref="AF2:AF17">
     <cfRule type="cellIs" dxfId="0" priority="30" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AG2:AG27">
+  <conditionalFormatting sqref="AG2:AG17">
     <cfRule type="cellIs" dxfId="0" priority="31" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH2:AH27">
+  <conditionalFormatting sqref="AH2:AH17">
     <cfRule type="cellIs" dxfId="0" priority="32" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI2:AI27">
+  <conditionalFormatting sqref="AI2:AI17">
     <cfRule type="cellIs" dxfId="0" priority="33" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AJ2:AJ27">
+  <conditionalFormatting sqref="AJ2:AJ17">
     <cfRule type="cellIs" dxfId="0" priority="34" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK2:AK27">
+  <conditionalFormatting sqref="AK2:AK17">
     <cfRule type="cellIs" dxfId="0" priority="35" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL2:AL27">
+  <conditionalFormatting sqref="AL2:AL17">
     <cfRule type="cellIs" dxfId="0" priority="36" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM2:AM27">
+  <conditionalFormatting sqref="AM2:AM17">
     <cfRule type="cellIs" dxfId="0" priority="37" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN2:AN27">
+  <conditionalFormatting sqref="AN2:AN17">
     <cfRule type="cellIs" dxfId="0" priority="38" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AO2:AO27">
+  <conditionalFormatting sqref="AO2:AO17">
     <cfRule type="cellIs" dxfId="0" priority="39" operator="equal">
       <formula>"No Evaluado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1014">
+  <conditionalFormatting sqref="AP2:AP17">
+    <cfRule type="cellIs" dxfId="0" priority="40" operator="equal">
+      <formula>"No Evaluado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AQ2:AQ17">
+    <cfRule type="cellIs" dxfId="0" priority="41" operator="equal">
+      <formula>"No Evaluado"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="656">
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA13">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA20">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA22">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA19">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA11">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA24">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA5">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
@@ -5137,9 +3986,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA17">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA27">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA8">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
@@ -5161,48 +4007,27 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA12">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA23">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA3">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA18">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA4">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA25">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA21">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA2">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA16">
       <formula1>Hoja2!$B$98:$B$101</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AA26">
-      <formula1>Hoja2!$B$98:$B$101</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB8">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB19">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB3">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB2">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB24">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB4">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
@@ -5212,9 +4037,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB13">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB21">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB15">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
@@ -5224,15 +4046,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB6">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB25">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB10">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB23">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB16">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
@@ -5242,69 +4058,33 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB7">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB27">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB22">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB26">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB17">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB5">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB20">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB9">
       <formula1>Hoja2!$B$102:$B$105</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AB18">
-      <formula1>Hoja2!$B$102:$B$105</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC12">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC21">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC13">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC23">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC18">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC5">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC19">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC14">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC4">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC27">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC22">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC7">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC24">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC15">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
@@ -5320,18 +4100,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC17">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC26">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC20">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC16">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC25">
-      <formula1>Hoja2!$B$106:$B$109</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC2">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
@@ -5344,9 +4115,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AC8">
       <formula1>Hoja2!$B$106:$B$109</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD23">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD14">
       <formula1>Hoja2!$B$110:$B$113</formula1>
     </dataValidation>
@@ -5356,36 +4124,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD9">
       <formula1>Hoja2!$B$110:$B$113</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD21">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD20">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD3">
       <formula1>Hoja2!$B$110:$B$113</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD19">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD22">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD5">
       <formula1>Hoja2!$B$110:$B$113</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD26">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD24">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD27">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD25">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD7">
       <formula1>Hoja2!$B$110:$B$113</formula1>
     </dataValidation>
@@ -5395,9 +4139,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD15">
       <formula1>Hoja2!$B$110:$B$113</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD18">
-      <formula1>Hoja2!$B$110:$B$113</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AD8">
       <formula1>Hoja2!$B$110:$B$113</formula1>
     </dataValidation>
@@ -5425,9 +4166,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE17">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE18">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE12">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
@@ -5440,42 +4178,21 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE8">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE20">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE15">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE23">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE25">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE9">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE10">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE21">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE16">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE26">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE19">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE11">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE24">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE3">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
@@ -5491,30 +4208,15 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE2">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE22">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE27">
-      <formula1>Hoja2!$B$114:$B$117</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AE5">
       <formula1>Hoja2!$B$114:$B$117</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF26">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF6">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF19">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF5">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF21">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF12">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
@@ -5542,9 +4244,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF4">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF22">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF13">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
@@ -5554,54 +4253,21 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF16">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF18">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF25">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF17">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF24">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF23">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF27">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF20">
-      <formula1>Hoja2!$B$118:$B$121</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AF2">
       <formula1>Hoja2!$B$118:$B$121</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG23">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG18">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG5">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG17">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG25">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG4">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG20">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG21">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG16">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
@@ -5614,27 +4280,18 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG11">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG27">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG7">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG10">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG26">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG13">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG12">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG19">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG15">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
@@ -5647,69 +4304,33 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG2">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG24">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG9">
       <formula1>Hoja2!$B$122:$B$125</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AG22">
-      <formula1>Hoja2!$B$122:$B$125</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH5">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH18">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH16">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH27">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH21">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH6">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH22">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH12">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH7">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH24">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH19">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH17">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH20">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH26">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH2">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH23">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH8">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH25">
-      <formula1>Hoja2!$B$126:$B$129</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH13">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
@@ -5734,18 +4355,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AH11">
       <formula1>Hoja2!$B$126:$B$129</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI27">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI12">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI8">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI26">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI9">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
@@ -5764,15 +4379,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI6">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI21">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI15">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI19">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI11">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
@@ -5782,54 +4391,24 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI13">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI24">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI17">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI3">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI22">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI25">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI23">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI16">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI18">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI20">
-      <formula1>Hoja2!$B$130:$B$133</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AI14">
       <formula1>Hoja2!$B$130:$B$133</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ24">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ18">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ13">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ25">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ16">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ19">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ3">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
@@ -5842,39 +4421,21 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ9">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ26">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ22">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ14">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ20">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ27">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ5">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ11">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ21">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ8">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ17">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ23">
-      <formula1>Hoja2!$B$134:$B$137</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AJ7">
       <formula1>Hoja2!$B$134:$B$137</formula1>
     </dataValidation>
@@ -5902,27 +4463,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK10">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK20">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK19">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK21">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK26">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK13">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK16">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK23">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK8">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
@@ -5932,9 +4478,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK2">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK27">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK12">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
@@ -5947,12 +4490,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK4">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK22">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK18">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK5">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
@@ -5962,42 +4499,18 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK15">
       <formula1>Hoja2!$B$138:$B$141</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK24">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AK25">
-      <formula1>Hoja2!$B$138:$B$141</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL24">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL13">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL4">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL22">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL19">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL23">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL14">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL20">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL2">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL18">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL12">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
@@ -6007,12 +4520,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL9">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL27">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL26">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL5">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
@@ -6034,54 +4541,27 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL3">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL21">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL16">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL25">
-      <formula1>Hoja2!$B$142:$B$145</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AL6">
       <formula1>Hoja2!$B$142:$B$145</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM6">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM25">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM13">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM27">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM16">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM24">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM2">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM22">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM4">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM19">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM21">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM20">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM3">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
@@ -6100,27 +4580,18 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM12">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM18">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM10">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM11">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM23">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM14">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM8">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM26">
-      <formula1>Hoja2!$B$146:$B$149</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AM15">
       <formula1>Hoja2!$B$146:$B$149</formula1>
     </dataValidation>
@@ -6133,9 +4604,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN17">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN27">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN14">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
@@ -6145,9 +4613,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN5">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN21">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN16">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
@@ -6160,42 +4625,18 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN15">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN20">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN12">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN6">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN19">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN8">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN24">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN22">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN9">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN23">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN18">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN25">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN26">
-      <formula1>Hoja2!$B$150:$B$153</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AN3">
       <formula1>Hoja2!$B$150:$B$153</formula1>
     </dataValidation>
@@ -6217,18 +4658,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO3">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO20">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO15">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO11">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO19">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO8">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
@@ -6238,50 +4673,119 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO7">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO24">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO10">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO25">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO22">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO27">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO13">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO23">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO12">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO2">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO21">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO18">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO9">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO26">
-      <formula1>Hoja2!$B$154:$B$157</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AO6">
       <formula1>Hoja2!$B$154:$B$157</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C26">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP3">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP5">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP2">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP7">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP9">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP14">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP8">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP15">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP10">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP12">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP17">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP13">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP6">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP4">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP11">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AP16">
+      <formula1>Hoja2!$B$158:$B$161</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ3">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ13">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ8">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ5">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ15">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ6">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ2">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ14">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ10">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ17">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ11">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ4">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ7">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ16">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ9">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="AQ12">
+      <formula1>Hoja2!$B$162:$B$165</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C14">
       <formula1>Hoja2!$B$2:$B$5</formula1>
@@ -6289,30 +4793,18 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C4">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C19">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C12">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C24">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C9">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C20">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C5">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C6">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C23">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C16">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
@@ -6331,33 +4823,18 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C8">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C25">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C18">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C15">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C7">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C22">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C17">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C10">
       <formula1>Hoja2!$B$2:$B$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C21">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="C27">
-      <formula1>Hoja2!$B$2:$B$5</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D13">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
@@ -6370,39 +4847,21 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D8">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D22">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D5">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D19">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D23">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D14">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D3">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D27">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D24">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D17">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D9">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D20">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D16">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
@@ -6418,84 +4877,45 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D4">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D26">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D18">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D2">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D11">
       <formula1>Hoja2!$B$6:$B$9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D25">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="D21">
-      <formula1>Hoja2!$B$6:$B$9</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E14">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E3">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E22">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E4">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E9">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E18">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E12">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E27">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E13">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E23">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E6">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E21">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E2">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E25">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E19">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E10">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E8">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E24">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E15">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E20">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E16">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
@@ -6508,33 +4928,18 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E11">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E26">
-      <formula1>Hoja2!$B$10:$B$13</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="E5">
       <formula1>Hoja2!$B$10:$B$13</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F8">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F27">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F26">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F6">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F2">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F18">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F19">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F14">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
@@ -6550,18 +4955,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F7">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F20">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F23">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F22">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F21">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F10">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
@@ -6571,18 +4964,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F13">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F25">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F11">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F16">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F24">
-      <formula1>Hoja2!$B$14:$B$17</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="F9">
       <formula1>Hoja2!$B$14:$B$17</formula1>
     </dataValidation>
@@ -6619,24 +5006,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G12">
       <formula1>Hoja2!$B$18:$B$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G24">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G18">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G19">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G5">
       <formula1>Hoja2!$B$18:$B$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G26">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G27">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G10">
       <formula1>Hoja2!$B$18:$B$21</formula1>
     </dataValidation>
@@ -6646,33 +5018,15 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G4">
       <formula1>Hoja2!$B$18:$B$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G25">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G21">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G20">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G16">
       <formula1>Hoja2!$B$18:$B$21</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G2">
       <formula1>Hoja2!$B$18:$B$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G23">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G6">
       <formula1>Hoja2!$B$18:$B$21</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="G22">
-      <formula1>Hoja2!$B$18:$B$21</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H21">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H11">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
@@ -6682,39 +5036,21 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H9">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H23">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H18">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H4">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H15">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H22">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H7">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H26">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H10">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H16">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H20">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H19">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H5">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
@@ -6724,9 +5060,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H8">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H25">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H12">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
@@ -6739,24 +5072,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H2">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H27">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H24">
-      <formula1>Hoja2!$B$22:$B$25</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="H17">
       <formula1>Hoja2!$B$22:$B$25</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I24">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I14">
       <formula1>Hoja2!$B$26:$B$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I22">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I10">
       <formula1>Hoja2!$B$26:$B$29</formula1>
     </dataValidation>
@@ -6778,18 +5099,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I12">
       <formula1>Hoja2!$B$26:$B$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I26">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I20">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I4">
       <formula1>Hoja2!$B$26:$B$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I23">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I17">
       <formula1>Hoja2!$B$26:$B$29</formula1>
     </dataValidation>
@@ -6808,27 +5120,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I2">
       <formula1>Hoja2!$B$26:$B$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I19">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I18">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I11">
       <formula1>Hoja2!$B$26:$B$29</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I27">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I21">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="I25">
-      <formula1>Hoja2!$B$26:$B$29</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J22">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J10">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
@@ -6838,12 +5132,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J12">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J24">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J25">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J5">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
@@ -6853,18 +5141,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J17">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J21">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J26">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J19">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J23">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J16">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
@@ -6874,9 +5150,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J4">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J18">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J9">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
@@ -6895,15 +5168,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J15">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J27">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J13">
       <formula1>Hoja2!$B$30:$B$33</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="J20">
-      <formula1>Hoja2!$B$30:$B$33</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K8">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
@@ -6925,12 +5192,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K14">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K19">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K22">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K13">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
@@ -6940,84 +5201,36 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K9">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K26">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K2">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K15">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K25">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K27">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K11">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K23">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K4">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K20">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K21">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K24">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K18">
-      <formula1>Hoja2!$B$34:$B$37</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K10">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="K6">
       <formula1>Hoja2!$B$34:$B$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L18">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L20">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L14">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L21">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L25">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L16">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L27">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L24">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L19">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L10">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L3">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L22">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L5">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
@@ -7027,15 +5240,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L6">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L26">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L9">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L23">
-      <formula1>Hoja2!$B$38:$B$41</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="L11">
       <formula1>Hoja2!$B$38:$B$41</formula1>
     </dataValidation>
@@ -7063,15 +5270,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M2">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M25">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M27">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M21">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M13">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
@@ -7087,9 +5285,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M12">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M20">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M3">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
@@ -7099,15 +5294,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M7">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M22">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M18">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M24">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M8">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
@@ -7120,15 +5306,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M6">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M26">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M23">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M19">
-      <formula1>Hoja2!$B$42:$B$45</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="M15">
       <formula1>Hoja2!$B$42:$B$45</formula1>
     </dataValidation>
@@ -7141,9 +5318,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N4">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N25">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N10">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
@@ -7153,9 +5327,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N3">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N24">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N16">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
@@ -7168,9 +5339,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N7">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N27">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N13">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
@@ -7180,24 +5348,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N5">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N22">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N21">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N18">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N14">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N26">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N23">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N17">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
@@ -7207,21 +5360,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N12">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N19">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N6">
       <formula1>Hoja2!$B$46:$B$49</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="N20">
-      <formula1>Hoja2!$B$46:$B$49</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O14">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O22">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O16">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
@@ -7231,15 +5375,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O4">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O20">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O8">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O25">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O17">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
@@ -7249,15 +5387,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O11">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O24">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O18">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O23">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O9">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
@@ -7276,33 +5405,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O5">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O21">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O12">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O26">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O7">
       <formula1>Hoja2!$B$50:$B$53</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O19">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="O27">
-      <formula1>Hoja2!$B$50:$B$53</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P22">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P27">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P20">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P5">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
@@ -7312,12 +5420,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P13">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P21">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P26">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P8">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
@@ -7333,9 +5435,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P15">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P24">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P14">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
@@ -7345,12 +5444,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P17">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P23">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P18">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P6">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
@@ -7363,15 +5456,9 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P4">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P19">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P7">
       <formula1>Hoja2!$B$54:$B$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="P25">
-      <formula1>Hoja2!$B$54:$B$57</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q14">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
@@ -7381,9 +5468,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q3">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q27">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q2">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
@@ -7393,24 +5477,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q11">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q26">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q8">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q18">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q5">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q22">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q20">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q7">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
@@ -7426,60 +5498,30 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q10">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q24">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q21">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q23">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q16">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q25">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q9">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q15">
       <formula1>Hoja2!$B$58:$B$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Q19">
-      <formula1>Hoja2!$B$58:$B$61</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R15">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R27">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R14">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R22">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R26">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R3">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R21">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R17">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R8">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R18">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R5">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
@@ -7492,15 +5534,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R6">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R19">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R20">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R24">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R10">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
@@ -7516,21 +5549,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R2">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R25">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R13">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R23">
-      <formula1>Hoja2!$B$62:$B$65</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="R12">
       <formula1>Hoja2!$B$62:$B$65</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S25">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S12">
       <formula1>Hoja2!$B$66:$B$69</formula1>
     </dataValidation>
@@ -7543,39 +5567,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S9">
       <formula1>Hoja2!$B$66:$B$69</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S22">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S3">
       <formula1>Hoja2!$B$66:$B$69</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S27">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S21">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S18">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S23">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S15">
       <formula1>Hoja2!$B$66:$B$69</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S24">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S19">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S20">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S26">
-      <formula1>Hoja2!$B$66:$B$69</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S2">
       <formula1>Hoja2!$B$66:$B$69</formula1>
     </dataValidation>
@@ -7606,9 +5603,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="S13">
       <formula1>Hoja2!$B$66:$B$69</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T20">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T17">
       <formula1>Hoja2!$B$70:$B$73</formula1>
     </dataValidation>
@@ -7648,21 +5642,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T16">
       <formula1>Hoja2!$B$70:$B$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T18">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T24">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T25">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T26">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T27">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T14">
       <formula1>Hoja2!$B$70:$B$73</formula1>
     </dataValidation>
@@ -7672,30 +5651,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T3">
       <formula1>Hoja2!$B$70:$B$73</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T21">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T22">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T19">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="T23">
-      <formula1>Hoja2!$B$70:$B$73</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U8">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U21">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U3">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U20">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U17">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
@@ -7717,21 +5678,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U14">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U24">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U22">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U4">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U13">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U26">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U15">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
@@ -7741,69 +5693,30 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U9">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U18">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U25">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U19">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U5">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U23">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U12">
       <formula1>Hoja2!$B$74:$B$77</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="U27">
-      <formula1>Hoja2!$B$74:$B$77</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V6">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V26">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V23">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V13">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V18">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V21">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V4">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V9">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V22">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V25">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V12">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V19">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V15">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V27">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V8">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
@@ -7813,12 +5726,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V10">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V24">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V20">
-      <formula1>Hoja2!$B$78:$B$81</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="V17">
       <formula1>Hoja2!$B$78:$B$81</formula1>
     </dataValidation>
@@ -7843,12 +5750,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W16">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W20">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W19">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W5">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
@@ -7861,27 +5762,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W8">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W26">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W27">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W18">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W6">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W14">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W22">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W24">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W4">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
@@ -7894,24 +5780,15 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W7">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W23">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W3">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W15">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W25">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W13">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W21">
-      <formula1>Hoja2!$B$82:$B$85</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="W11">
       <formula1>Hoja2!$B$82:$B$85</formula1>
     </dataValidation>
@@ -7933,75 +5810,42 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X8">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X23">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X5">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X21">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X17">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X13">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X19">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X26">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X6">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X11">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X18">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X24">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X10">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X2">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X27">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X9">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X16">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X22">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X7">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X12">
       <formula1>Hoja2!$B$86:$B$89</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X20">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="X25">
-      <formula1>Hoja2!$B$86:$B$89</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y13">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y22">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y16">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
@@ -8017,21 +5861,6 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y10">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y18">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y19">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y24">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y20">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y26">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y5">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
@@ -8047,24 +5876,12 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y12">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y27">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y8">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y7">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y25">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y23">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y21">
-      <formula1>Hoja2!$B$90:$B$93</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Y11">
       <formula1>Hoja2!$B$90:$B$93</formula1>
     </dataValidation>
@@ -8083,64 +5900,34 @@
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z4">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z21">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z8">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z19">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z23">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z5">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z16">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z18">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z14">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z24">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z2">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z22">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z11">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z27">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z17">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z15">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z26">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z25">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z6">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z13">
-      <formula1>Hoja2!$B$94:$B$97</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z20">
       <formula1>Hoja2!$B$94:$B$97</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" sqref="Z9">
@@ -8173,7 +5960,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C157"/>
+  <dimension ref="A1:C165"/>
   <sheetFormatPr customHeight="true" defaultRowHeight="35" defaultColWidth="11.5703125" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="true" style="1"/>
@@ -8183,44 +5970,44 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" customHeight="1" ht="25.5">
       <c r="A2" s="13" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:3" customHeight="1" ht="25.5">
       <c r="A3" s="13" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C3" s="15"/>
     </row>
-    <row r="4" spans="1:3" customHeight="1" ht="25.5">
+    <row r="4" spans="1:3">
       <c r="A4" s="13" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C4" s="15"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="13" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>0</v>
@@ -8229,36 +6016,36 @@
     </row>
     <row r="6" spans="1:3" customHeight="1" ht="25.5">
       <c r="A6" s="14" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" customHeight="1" ht="25.5">
       <c r="A7" s="14" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C7" s="16"/>
     </row>
     <row r="8" spans="1:3" customHeight="1" ht="25.5">
       <c r="A8" s="14" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C8" s="16"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="14" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B9" s="14" t="s">
         <v>0</v>
@@ -8267,36 +6054,36 @@
     </row>
     <row r="10" spans="1:3" customHeight="1" ht="25.5">
       <c r="A10" s="13" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:3" customHeight="1" ht="25.5">
       <c r="A11" s="13" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C11" s="15"/>
     </row>
     <row r="12" spans="1:3" customHeight="1" ht="25.5">
       <c r="A12" s="13" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C12" s="15"/>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="13" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B13" s="13" t="s">
         <v>0</v>
@@ -8305,74 +6092,74 @@
     </row>
     <row r="14" spans="1:3" customHeight="1" ht="25.5">
       <c r="A14" s="14" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" customHeight="1" ht="25.5">
       <c r="A15" s="14" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C15" s="16"/>
     </row>
     <row r="16" spans="1:3" customHeight="1" ht="25.5">
       <c r="A16" s="14" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C16" s="16"/>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="14" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B17" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C17" s="16"/>
     </row>
-    <row r="18" spans="1:3" customHeight="1" ht="51">
+    <row r="18" spans="1:3" customHeight="1" ht="25.5">
       <c r="A18" s="13" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" customHeight="1" ht="25.5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
       <c r="A19" s="13" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C19" s="15"/>
     </row>
-    <row r="20" spans="1:3" customHeight="1" ht="25.5">
+    <row r="20" spans="1:3">
       <c r="A20" s="13" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C20" s="15"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="13" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B21" s="13" t="s">
         <v>0</v>
@@ -8381,36 +6168,36 @@
     </row>
     <row r="22" spans="1:3" customHeight="1" ht="25.5">
       <c r="A22" s="14" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" customHeight="1" ht="25.5">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="A23" s="14" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C23" s="16"/>
     </row>
     <row r="24" spans="1:3" customHeight="1" ht="25.5">
       <c r="A24" s="14" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B24" s="14" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C24" s="16"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="14" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B25" s="14" t="s">
         <v>0</v>
@@ -8419,36 +6206,36 @@
     </row>
     <row r="26" spans="1:3" customHeight="1" ht="25.5">
       <c r="A26" s="13" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" customHeight="1" ht="38.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" customHeight="1" ht="25.5">
       <c r="A27" s="13" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C27" s="15"/>
     </row>
     <row r="28" spans="1:3" customHeight="1" ht="25.5">
       <c r="A28" s="13" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C28" s="15"/>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="13" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="B29" s="13" t="s">
         <v>0</v>
@@ -8457,36 +6244,36 @@
     </row>
     <row r="30" spans="1:3" customHeight="1" ht="25.5">
       <c r="A30" s="14" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:3" customHeight="1" ht="25.5">
       <c r="A31" s="14" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C31" s="16"/>
     </row>
     <row r="32" spans="1:3" customHeight="1" ht="25.5">
       <c r="A32" s="14" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C32" s="16"/>
     </row>
     <row r="33" spans="1:3">
       <c r="A33" s="14" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="B33" s="14" t="s">
         <v>0</v>
@@ -8495,36 +6282,36 @@
     </row>
     <row r="34" spans="1:3" customHeight="1" ht="25.5">
       <c r="A34" s="13" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C34" s="15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:3" customHeight="1" ht="25.5">
       <c r="A35" s="13" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C35" s="15"/>
     </row>
-    <row r="36" spans="1:3" customHeight="1" ht="25.5">
+    <row r="36" spans="1:3">
       <c r="A36" s="13" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C36" s="15"/>
     </row>
     <row r="37" spans="1:3">
       <c r="A37" s="13" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B37" s="13" t="s">
         <v>0</v>
@@ -8533,36 +6320,36 @@
     </row>
     <row r="38" spans="1:3">
       <c r="A38" s="14" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:3" customHeight="1" ht="25.5">
       <c r="A39" s="14" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C39" s="16"/>
     </row>
-    <row r="40" spans="1:3" customHeight="1" ht="25.5">
+    <row r="40" spans="1:3">
       <c r="A40" s="14" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B40" s="14" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C40" s="16"/>
     </row>
     <row r="41" spans="1:3">
       <c r="A41" s="14" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="B41" s="14" t="s">
         <v>0</v>
@@ -8571,36 +6358,36 @@
     </row>
     <row r="42" spans="1:3" customHeight="1" ht="25.5">
       <c r="A42" s="13" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C42" s="15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:3" customHeight="1" ht="25.5">
       <c r="A43" s="13" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C43" s="15"/>
     </row>
     <row r="44" spans="1:3" customHeight="1" ht="25.5">
       <c r="A44" s="13" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="C44" s="15"/>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="13" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B45" s="13" t="s">
         <v>0</v>
@@ -8609,36 +6396,36 @@
     </row>
     <row r="46" spans="1:3" customHeight="1" ht="25.5">
       <c r="A46" s="14" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B46" s="14" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" customHeight="1" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
       <c r="A47" s="14" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B47" s="14" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="C47" s="16"/>
     </row>
-    <row r="48" spans="1:3" customHeight="1" ht="25.5">
+    <row r="48" spans="1:3">
       <c r="A48" s="14" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C48" s="16"/>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" s="14" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B49" s="14" t="s">
         <v>0</v>
@@ -8647,74 +6434,74 @@
     </row>
     <row r="50" spans="1:3" customHeight="1" ht="25.5">
       <c r="A50" s="13" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="C50" s="15" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="51" spans="1:3" customHeight="1" ht="25.5">
       <c r="A51" s="13" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="C51" s="15"/>
     </row>
     <row r="52" spans="1:3" customHeight="1" ht="25.5">
       <c r="A52" s="13" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="C52" s="15"/>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="13" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B53" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C53" s="15"/>
     </row>
-    <row r="54" spans="1:3" customHeight="1" ht="25.5">
+    <row r="54" spans="1:3">
       <c r="A54" s="14" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B54" s="14" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" customHeight="1" ht="38.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="14" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C55" s="16"/>
     </row>
-    <row r="56" spans="1:3" customHeight="1" ht="38.25">
+    <row r="56" spans="1:3" customHeight="1" ht="25.5">
       <c r="A56" s="14" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="B56" s="14" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="C56" s="16"/>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" s="14" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="B57" s="14" t="s">
         <v>0</v>
@@ -8723,112 +6510,112 @@
     </row>
     <row r="58" spans="1:3" customHeight="1" ht="25.5">
       <c r="A58" s="13" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:3" customHeight="1" ht="25.5">
       <c r="A59" s="13" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="C59" s="15"/>
     </row>
-    <row r="60" spans="1:3">
+    <row r="60" spans="1:3" customHeight="1" ht="25.5">
       <c r="A60" s="13" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C60" s="15"/>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" s="13" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B61" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C61" s="15"/>
     </row>
-    <row r="62" spans="1:3" customHeight="1" ht="38.25">
+    <row r="62" spans="1:3" customHeight="1" ht="25.5">
       <c r="A62" s="14" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="B62" s="14" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:3" customHeight="1" ht="25.5">
       <c r="A63" s="14" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="B63" s="14" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C63" s="16"/>
     </row>
     <row r="64" spans="1:3">
       <c r="A64" s="14" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="B64" s="14" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="C64" s="16"/>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="14" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="B65" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C65" s="16"/>
     </row>
-    <row r="66" spans="1:3" customHeight="1" ht="51">
+    <row r="66" spans="1:3" customHeight="1" ht="25.5">
       <c r="A66" s="13" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" customHeight="1" ht="38.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" customHeight="1" ht="25.5">
       <c r="A67" s="13" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="B67" s="13" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="C67" s="15"/>
     </row>
     <row r="68" spans="1:3" customHeight="1" ht="25.5">
       <c r="A68" s="13" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="C68" s="15"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="13" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="B69" s="13" t="s">
         <v>0</v>
@@ -8837,74 +6624,74 @@
     </row>
     <row r="70" spans="1:3" customHeight="1" ht="25.5">
       <c r="A70" s="14" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="B70" s="14" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" customHeight="1" ht="38.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
       <c r="A71" s="14" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B71" s="14" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="C71" s="16"/>
     </row>
     <row r="72" spans="1:3" customHeight="1" ht="25.5">
       <c r="A72" s="14" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B72" s="14" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="C72" s="16"/>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="14" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C73" s="16"/>
     </row>
-    <row r="74" spans="1:3" customHeight="1" ht="25.5">
+    <row r="74" spans="1:3" customHeight="1" ht="38.25">
       <c r="A74" s="13" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C74" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" customHeight="1" ht="25.5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
       <c r="A75" s="13" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B75" s="13" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="C75" s="15"/>
     </row>
-    <row r="76" spans="1:3" customHeight="1" ht="38.25">
+    <row r="76" spans="1:3" customHeight="1" ht="25.5">
       <c r="A76" s="13" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="C76" s="15"/>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="13" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B77" s="13" t="s">
         <v>0</v>
@@ -8913,74 +6700,74 @@
     </row>
     <row r="78" spans="1:3" customHeight="1" ht="25.5">
       <c r="A78" s="14" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B78" s="14" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79" spans="1:3" customHeight="1" ht="25.5">
       <c r="A79" s="14" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="C79" s="16"/>
     </row>
     <row r="80" spans="1:3" customHeight="1" ht="25.5">
       <c r="A80" s="14" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B80" s="14" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="C80" s="16"/>
     </row>
     <row r="81" spans="1:3">
       <c r="A81" s="14" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="B81" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C81" s="16"/>
     </row>
-    <row r="82" spans="1:3" customHeight="1" ht="25.5">
+    <row r="82" spans="1:3" customHeight="1" ht="38.25">
       <c r="A82" s="13" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="C82" s="15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="1:3" customHeight="1" ht="25.5">
       <c r="A83" s="13" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="C83" s="15"/>
     </row>
     <row r="84" spans="1:3" customHeight="1" ht="25.5">
       <c r="A84" s="13" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="C84" s="15"/>
     </row>
     <row r="85" spans="1:3">
       <c r="A85" s="13" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="B85" s="13" t="s">
         <v>0</v>
@@ -8989,36 +6776,36 @@
     </row>
     <row r="86" spans="1:3">
       <c r="A86" s="14" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B86" s="14" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" customHeight="1" ht="25.5">
       <c r="A87" s="14" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B87" s="14" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C87" s="16"/>
     </row>
-    <row r="88" spans="1:3">
+    <row r="88" spans="1:3" customHeight="1" ht="25.5">
       <c r="A88" s="14" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="B88" s="14" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="C88" s="16"/>
     </row>
     <row r="89" spans="1:3">
       <c r="A89" s="14" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="B89" s="14" t="s">
         <v>0</v>
@@ -9027,74 +6814,74 @@
     </row>
     <row r="90" spans="1:3">
       <c r="A90" s="13" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="C90" s="15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:3" customHeight="1" ht="25.5">
       <c r="A91" s="13" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="B91" s="13" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C91" s="15"/>
     </row>
-    <row r="92" spans="1:3">
+    <row r="92" spans="1:3" customHeight="1" ht="25.5">
       <c r="A92" s="13" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C92" s="15"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="13" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="B93" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C93" s="15"/>
     </row>
-    <row r="94" spans="1:3" customHeight="1" ht="25.5">
+    <row r="94" spans="1:3">
       <c r="A94" s="14" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="B94" s="14" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:3" customHeight="1" ht="25.5">
       <c r="A95" s="14" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B95" s="14" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="C95" s="16"/>
     </row>
-    <row r="96" spans="1:3" customHeight="1" ht="25.5">
+    <row r="96" spans="1:3">
       <c r="A96" s="14" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B96" s="14" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="C96" s="16"/>
     </row>
     <row r="97" spans="1:3">
       <c r="A97" s="14" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="B97" s="14" t="s">
         <v>0</v>
@@ -9103,74 +6890,74 @@
     </row>
     <row r="98" spans="1:3">
       <c r="A98" s="13" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="C98" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" customHeight="1" ht="25.5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="13" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B99" s="13" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="C99" s="15"/>
     </row>
     <row r="100" spans="1:3">
       <c r="A100" s="13" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C100" s="15"/>
     </row>
     <row r="101" spans="1:3">
       <c r="A101" s="13" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="B101" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C101" s="15"/>
     </row>
-    <row r="102" spans="1:3" customHeight="1" ht="25.5">
+    <row r="102" spans="1:3">
       <c r="A102" s="14" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="B102" s="14" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" customHeight="1" ht="25.5">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
       <c r="A103" s="14" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B103" s="14" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="C103" s="16"/>
     </row>
     <row r="104" spans="1:3" customHeight="1" ht="25.5">
       <c r="A104" s="14" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B104" s="14" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="C104" s="16"/>
     </row>
     <row r="105" spans="1:3">
       <c r="A105" s="14" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="B105" s="14" t="s">
         <v>0</v>
@@ -9179,150 +6966,150 @@
     </row>
     <row r="106" spans="1:3">
       <c r="A106" s="13" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="C106" s="15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" customHeight="1" ht="25.5">
       <c r="A107" s="13" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="B107" s="13" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="C107" s="15"/>
     </row>
     <row r="108" spans="1:3" customHeight="1" ht="25.5">
       <c r="A108" s="13" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="C108" s="15"/>
     </row>
     <row r="109" spans="1:3">
       <c r="A109" s="13" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="B109" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C109" s="15"/>
     </row>
-    <row r="110" spans="1:3" customHeight="1" ht="25.5">
+    <row r="110" spans="1:3">
       <c r="A110" s="14" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="B110" s="14" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" customHeight="1" ht="25.5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
       <c r="A111" s="14" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="B111" s="14" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="C111" s="16"/>
     </row>
-    <row r="112" spans="1:3" customHeight="1" ht="25.5">
+    <row r="112" spans="1:3">
       <c r="A112" s="14" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="B112" s="14" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="C112" s="16"/>
     </row>
     <row r="113" spans="1:3">
       <c r="A113" s="14" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="B113" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C113" s="16"/>
     </row>
-    <row r="114" spans="1:3" customHeight="1" ht="25.5">
+    <row r="114" spans="1:3">
       <c r="A114" s="13" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="C114" s="15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" customHeight="1" ht="25.5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
       <c r="A115" s="13" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="B115" s="13" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="C115" s="15"/>
     </row>
-    <row r="116" spans="1:3" customHeight="1" ht="25.5">
+    <row r="116" spans="1:3">
       <c r="A116" s="13" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C116" s="15"/>
     </row>
     <row r="117" spans="1:3">
       <c r="A117" s="13" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B117" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C117" s="15"/>
     </row>
-    <row r="118" spans="1:3" customHeight="1" ht="25.5">
+    <row r="118" spans="1:3">
       <c r="A118" s="14" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B118" s="14" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C118" s="16" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" customHeight="1" ht="25.5">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" customHeight="1" ht="38.25">
       <c r="A119" s="14" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="B119" s="14" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="C119" s="16"/>
     </row>
-    <row r="120" spans="1:3" customHeight="1" ht="25.5">
+    <row r="120" spans="1:3">
       <c r="A120" s="14" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B120" s="14" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="C120" s="16"/>
     </row>
     <row r="121" spans="1:3">
       <c r="A121" s="14" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B121" s="14" t="s">
         <v>0</v>
@@ -9331,36 +7118,36 @@
     </row>
     <row r="122" spans="1:3" customHeight="1" ht="25.5">
       <c r="A122" s="13" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C122" s="15" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:3" customHeight="1" ht="25.5">
       <c r="A123" s="13" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="C123" s="15"/>
     </row>
-    <row r="124" spans="1:3" customHeight="1" ht="25.5">
+    <row r="124" spans="1:3" customHeight="1" ht="38.25">
       <c r="A124" s="13" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="C124" s="15"/>
     </row>
     <row r="125" spans="1:3">
       <c r="A125" s="13" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="B125" s="13" t="s">
         <v>0</v>
@@ -9369,36 +7156,36 @@
     </row>
     <row r="126" spans="1:3">
       <c r="A126" s="14" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="B126" s="14" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="C126" s="16" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" customHeight="1" ht="25.5">
       <c r="A127" s="14" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B127" s="14" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C127" s="16"/>
     </row>
     <row r="128" spans="1:3">
       <c r="A128" s="14" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="B128" s="14" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="C128" s="16"/>
     </row>
     <row r="129" spans="1:3">
       <c r="A129" s="14" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="B129" s="14" t="s">
         <v>0</v>
@@ -9407,74 +7194,74 @@
     </row>
     <row r="130" spans="1:3">
       <c r="A130" s="13" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C130" s="15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" customHeight="1" ht="25.5">
       <c r="A131" s="13" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="B131" s="13" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="C131" s="15"/>
     </row>
-    <row r="132" spans="1:3">
+    <row r="132" spans="1:3" customHeight="1" ht="25.5">
       <c r="A132" s="13" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="C132" s="15"/>
     </row>
     <row r="133" spans="1:3">
       <c r="A133" s="13" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B133" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C133" s="15"/>
     </row>
-    <row r="134" spans="1:3">
+    <row r="134" spans="1:3" customHeight="1" ht="25.5">
       <c r="A134" s="14" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B134" s="14" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="C134" s="16" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:3" customHeight="1" ht="25.5">
       <c r="A135" s="14" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B135" s="14" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="C135" s="16"/>
     </row>
     <row r="136" spans="1:3">
       <c r="A136" s="14" t="s">
-        <v>305</v>
+        <v>294</v>
       </c>
       <c r="B136" s="14" t="s">
-        <v>306</v>
+        <v>295</v>
       </c>
       <c r="C136" s="16"/>
     </row>
     <row r="137" spans="1:3">
       <c r="A137" s="14" t="s">
-        <v>307</v>
+        <v>296</v>
       </c>
       <c r="B137" s="14" t="s">
         <v>0</v>
@@ -9483,74 +7270,74 @@
     </row>
     <row r="138" spans="1:3">
       <c r="A138" s="13" t="s">
-        <v>308</v>
+        <v>297</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>309</v>
+        <v>298</v>
       </c>
       <c r="C138" s="15" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:3">
       <c r="A139" s="13" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="B139" s="13" t="s">
-        <v>311</v>
+        <v>300</v>
       </c>
       <c r="C139" s="15"/>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="13" t="s">
-        <v>312</v>
+        <v>301</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>313</v>
+        <v>302</v>
       </c>
       <c r="C140" s="15"/>
     </row>
     <row r="141" spans="1:3">
       <c r="A141" s="13" t="s">
-        <v>314</v>
+        <v>303</v>
       </c>
       <c r="B141" s="13" t="s">
         <v>0</v>
       </c>
       <c r="C141" s="15"/>
     </row>
-    <row r="142" spans="1:3" customHeight="1" ht="25.5">
+    <row r="142" spans="1:3">
       <c r="A142" s="14" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="B142" s="14" t="s">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="C142" s="16" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:3">
       <c r="A143" s="14" t="s">
-        <v>317</v>
+        <v>306</v>
       </c>
       <c r="B143" s="14" t="s">
-        <v>318</v>
+        <v>307</v>
       </c>
       <c r="C143" s="16"/>
     </row>
     <row r="144" spans="1:3">
       <c r="A144" s="14" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
       <c r="B144" s="14" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="C144" s="16"/>
     </row>
     <row r="145" spans="1:3">
       <c r="A145" s="14" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="B145" s="14" t="s">
         <v>0</v>
@@ -9559,36 +7346,36 @@
     </row>
     <row r="146" spans="1:3">
       <c r="A146" s="13" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="C146" s="15" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:3">
       <c r="A147" s="13" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="B147" s="13" t="s">
-        <v>325</v>
+        <v>314</v>
       </c>
       <c r="C147" s="15"/>
     </row>
     <row r="148" spans="1:3" customHeight="1" ht="25.5">
       <c r="A148" s="13" t="s">
-        <v>326</v>
+        <v>315</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="C148" s="15"/>
     </row>
     <row r="149" spans="1:3">
       <c r="A149" s="13" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="B149" s="13" t="s">
         <v>0</v>
@@ -9597,79 +7384,155 @@
     </row>
     <row r="150" spans="1:3" customHeight="1" ht="25.5">
       <c r="A150" s="14" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B150" s="14" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" customHeight="1" ht="25.5">
       <c r="A151" s="14" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="B151" s="14" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="C151" s="16"/>
     </row>
     <row r="152" spans="1:3">
       <c r="A152" s="14" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="B152" s="14" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="C152" s="16"/>
     </row>
     <row r="153" spans="1:3">
       <c r="A153" s="14" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="B153" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C153" s="16"/>
     </row>
-    <row r="154" spans="1:3">
+    <row r="154" spans="1:3" customHeight="1" ht="25.5">
       <c r="A154" s="13" t="s">
-        <v>336</v>
+        <v>325</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="C154" s="15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" customHeight="1" ht="25.5">
       <c r="A155" s="13" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="B155" s="13" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="C155" s="15"/>
     </row>
-    <row r="156" spans="1:3" customHeight="1" ht="25.5">
+    <row r="156" spans="1:3">
       <c r="A156" s="13" t="s">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="C156" s="15"/>
     </row>
     <row r="157" spans="1:3">
       <c r="A157" s="13" t="s">
+        <v>331</v>
+      </c>
+      <c r="B157" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C157" s="15"/>
+    </row>
+    <row r="158" spans="1:3" customHeight="1" ht="25.5">
+      <c r="A158" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="B158" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" customHeight="1" ht="25.5">
+      <c r="A159" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="B159" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="C159" s="16"/>
+    </row>
+    <row r="160" spans="1:3" customHeight="1" ht="25.5">
+      <c r="A160" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="B160" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="C160" s="16"/>
+    </row>
+    <row r="161" spans="1:3">
+      <c r="A161" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="B161" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C161" s="16"/>
+    </row>
+    <row r="162" spans="1:3" customHeight="1" ht="25.5">
+      <c r="A162" s="13" t="s">
+        <v>339</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="C162" s="15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" customHeight="1" ht="25.5">
+      <c r="A163" s="13" t="s">
+        <v>341</v>
+      </c>
+      <c r="B163" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="B157" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C157" s="15"/>
+      <c r="C163" s="15"/>
+    </row>
+    <row r="164" spans="1:3" customHeight="1" ht="25.5">
+      <c r="A164" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="B164" s="13" t="s">
+        <v>344</v>
+      </c>
+      <c r="C164" s="15"/>
+    </row>
+    <row r="165" spans="1:3">
+      <c r="A165" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="B165" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C165" s="15"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
@@ -9713,6 +7576,8 @@
     <mergeCell ref="C146:C149"/>
     <mergeCell ref="C150:C153"/>
     <mergeCell ref="C154:C157"/>
+    <mergeCell ref="C158:C161"/>
+    <mergeCell ref="C162:C165"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>

--- a/php_libs/soporte/Herramientas/temp_excel_.xlsx
+++ b/php_libs/soporte/Herramientas/temp_excel_.xlsx
@@ -21,7 +21,7 @@
     <t>No Evaluado</t>
   </si>
   <si>
-    <t>ACEVEDO SERMEÑO, MADELINE ISABELLA</t>
+    <t>ASENCIO MORALES, ANTONY EZEQUIEL</t>
   </si>
   <si>
     <t>Cuidar de sí mismo identificando aquellas acciones, alimentos y hábitos que le generan bienestar, al mismo tiempo que incorpora algunas prácticas de reutilización de materiales y separación de desechos sólidos siempre que le sea posible, contribuyendo al cuidado colectivo de su comunidad.</t>
@@ -147,79 +147,79 @@
     <t>Código NIE</t>
   </si>
   <si>
-    <t>Alvarado Santos, Leilany Rebeca</t>
-  </si>
-  <si>
-    <t>ASENCIO GONZALEZ, JARED GABRIEL</t>
-  </si>
-  <si>
-    <t>BELTRAN BELTRAN, JOHAN CAMILO</t>
-  </si>
-  <si>
-    <t>BELTRAN BELTRAN, KILIAN OSMAR</t>
-  </si>
-  <si>
-    <t>CABRERA MARTÍNEZ, ALEJANDRO MAURICIO</t>
-  </si>
-  <si>
-    <t>CALDERON LOPEZ, DYLAN EZEQUIEL</t>
-  </si>
-  <si>
-    <t>CALIDONIO CRUZ, RONALD GEOVANNY</t>
-  </si>
-  <si>
-    <t>CHAVEZ AZAMA, ISAAC ALEXANDER</t>
-  </si>
-  <si>
-    <t>CHAVEZ RECINOS, JORGE ANDRE</t>
-  </si>
-  <si>
-    <t>ESCARATE MARTÍNEZ, GÉNESIS DAMARIS</t>
-  </si>
-  <si>
-    <t>GONAZALEZ LEIVA, WENDY ZULEYMA</t>
-  </si>
-  <si>
-    <t>JACO HERRERA, MICHAEL GAEL</t>
-  </si>
-  <si>
-    <t>MURILLO DIAZ, PRISCILA VICTORIA</t>
-  </si>
-  <si>
-    <t>PALMA VASQUEZ, MATEO EZEQUIEL</t>
-  </si>
-  <si>
-    <t>POLANCO IRAHETA, AXEL ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAMIREZ MANCIA, LUCAS ANTONIO</t>
-  </si>
-  <si>
-    <t>RECINOS MENDEZ, VALENTINA NICOLE</t>
-  </si>
-  <si>
-    <t>RIVAS FLORES, JOSUE CALEB</t>
-  </si>
-  <si>
-    <t>SANTOS CRUZ, JOSE ISAI</t>
-  </si>
-  <si>
-    <t>SANTOS DE LA CRUZ, MATTHEW ALESSANDRO</t>
-  </si>
-  <si>
-    <t>SIGUENZA CARIAS, JOSE ALEXANDER</t>
-  </si>
-  <si>
-    <t>SOLIS COLOCHO, NATALIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>VALDES VEGA, ALISSON SAMANTA</t>
-  </si>
-  <si>
-    <t>VALDEZ MARTÍNEZ, DENIS ULISES</t>
-  </si>
-  <si>
-    <t>ZARCEÑO HERRERA, KIMBERLY ROXANA</t>
+    <t>BARRERA MURCIA, MARJORIE ISABEL</t>
+  </si>
+  <si>
+    <t>COLOCHO SALGADO, AVRIL ALESSANDRA</t>
+  </si>
+  <si>
+    <t>DIAZ VASQUEZ, MAURICIO EZEQUIEL</t>
+  </si>
+  <si>
+    <t>ESTRADA PORTILLO, AYLEN ALESSANDRRA</t>
+  </si>
+  <si>
+    <t>FLORES LINARES, ROCIO ELIZABETH</t>
+  </si>
+  <si>
+    <t>GARCÍA AGUILAR, ÁNGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>GÓMEZ MARTÍNEZ, ALAN GAEL</t>
+  </si>
+  <si>
+    <t>GOMEZ VALDÉZ, EDUARDO ALEXANDER</t>
+  </si>
+  <si>
+    <t>GONZALEZ LANDAVERDE, AXEL CALEB</t>
+  </si>
+  <si>
+    <t>GUEVARA ARGUELLO, AXEL MATEO</t>
+  </si>
+  <si>
+    <t>GUIROLA MUNGUIA, JAFET ALEJANDRO</t>
+  </si>
+  <si>
+    <t>GUTIÉRREZ CARRANZA, GUDIEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>HENRÍQUEZ BELTRÁN, LIAM ESAÚ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ RUIZ, GISELA NATASHA</t>
+  </si>
+  <si>
+    <t>HERNÁNDEZ SANTOS, ALEXANDER YUMALAY</t>
+  </si>
+  <si>
+    <t>JACO ESCOBAR, ADRIAN EMANUEL</t>
+  </si>
+  <si>
+    <t>LOPEZ ENAMORADO, JOSUE ANTONIO</t>
+  </si>
+  <si>
+    <t>MARROQUIN GARCIA, KEYRI NICOL</t>
+  </si>
+  <si>
+    <t>MARTÍNEZ CASOVERDE, DIEGO SEBASTIAN</t>
+  </si>
+  <si>
+    <t>MARTÍNEZ GARCIA, JEREMY ISAI</t>
+  </si>
+  <si>
+    <t>MELARA ESTRADA, OSCAR ALESSANDRO</t>
+  </si>
+  <si>
+    <t>MENDOZA MAZARIEGO, MEGAN SCARLETH</t>
+  </si>
+  <si>
+    <t>MENJIVAR FLORES, ESTEFANI SOFIA</t>
+  </si>
+  <si>
+    <t>PINEDA PEÑATE, FERNANDO VLADIMIR</t>
+  </si>
+  <si>
+    <t>VINDEL MEDINA, ÁNGEL MATEO</t>
   </si>
   <si>
     <t>ID</t>
@@ -315,7 +315,7 @@
     <t>DP1-PG-05-A</t>
   </si>
   <si>
-    <t>Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.</t>
+    <t>Participa activamente en juegos y actividades grupales, mostrando disposición para cooperar y resolver desacuerdos mediante el diálogo, la negociación y el establecimiento de acuerdos.</t>
   </si>
   <si>
     <t>DP1-PG-05-B</t>
@@ -1534,7 +1534,7 @@
     <col min="40" max="40" width="28.140625" customWidth="true" style="0"/>
     <col min="41" max="41" width="28.140625" customWidth="true" style="0"/>
     <col min="1" max="1" width="12" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="43" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="42" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:41" customHeight="1" ht="149.25">
@@ -1664,7 +1664,7 @@
     </row>
     <row r="2" spans="1:41" customHeight="1" ht="60">
       <c r="A2" s="5">
-        <v>10782664</v>
+        <v>10925922</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>1</v>
@@ -1789,7 +1789,7 @@
     </row>
     <row r="3" spans="1:41" customHeight="1" ht="60">
       <c r="A3" s="7">
-        <v>10557767</v>
+        <v>10750612</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>43</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="4" spans="1:41" customHeight="1" ht="60">
       <c r="A4" s="5">
-        <v>11096587</v>
+        <v>10750714</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>44</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="5" spans="1:41" customHeight="1" ht="60">
       <c r="A5" s="7">
-        <v>10662107</v>
+        <v>10795897</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>45</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="6" spans="1:41" customHeight="1" ht="60">
       <c r="A6" s="5">
-        <v>10662114</v>
+        <v>10867955</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>46</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="7" spans="1:41" customHeight="1" ht="60">
       <c r="A7" s="7">
-        <v>10730806</v>
+        <v>10761974</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>47</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="8" spans="1:41" customHeight="1" ht="60">
       <c r="A8" s="5">
-        <v>10744414</v>
+        <v>10768977</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>48</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="9" spans="1:41" customHeight="1" ht="60">
       <c r="A9" s="7">
-        <v>10891577</v>
+        <v>10933181</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>49</v>
@@ -2664,7 +2664,7 @@
     </row>
     <row r="10" spans="1:41" customHeight="1" ht="60">
       <c r="A10" s="5">
-        <v>10740232</v>
+        <v>10933196</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>50</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="11" spans="1:41" customHeight="1" ht="60">
       <c r="A11" s="7">
-        <v>11039874</v>
+        <v>10755515</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>51</v>
@@ -2914,7 +2914,7 @@
     </row>
     <row r="12" spans="1:41" customHeight="1" ht="60">
       <c r="A12" s="5">
-        <v>10744557</v>
+        <v>10750762</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>52</v>
@@ -3039,7 +3039,7 @@
     </row>
     <row r="13" spans="1:41" customHeight="1" ht="60">
       <c r="A13" s="7">
-        <v>11182811</v>
+        <v>10607644</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>53</v>
@@ -3164,7 +3164,7 @@
     </row>
     <row r="14" spans="1:41" customHeight="1" ht="60">
       <c r="A14" s="5">
-        <v>10762549</v>
+        <v>10750804</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>54</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="15" spans="1:41" customHeight="1" ht="60">
       <c r="A15" s="7">
-        <v>11027602</v>
+        <v>10607405</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>55</v>
@@ -3414,7 +3414,7 @@
     </row>
     <row r="16" spans="1:41" customHeight="1" ht="60">
       <c r="A16" s="5">
-        <v>10878662</v>
+        <v>10750853</v>
       </c>
       <c r="B16" s="9" t="s">
         <v>56</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="17" spans="1:41" customHeight="1" ht="60">
       <c r="A17" s="7">
-        <v>10803817</v>
+        <v>10933662</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>57</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="18" spans="1:41" customHeight="1" ht="60">
       <c r="A18" s="5">
-        <v>10751410</v>
+        <v>10935383</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>58</v>
@@ -3789,7 +3789,7 @@
     </row>
     <row r="19" spans="1:41" customHeight="1" ht="60">
       <c r="A19" s="7">
-        <v>10869391</v>
+        <v>10750890</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>59</v>
@@ -3914,7 +3914,7 @@
     </row>
     <row r="20" spans="1:41" customHeight="1" ht="60">
       <c r="A20" s="5">
-        <v>10541138</v>
+        <v>10750909</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>60</v>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="21" spans="1:41" customHeight="1" ht="60">
       <c r="A21" s="7">
-        <v>10554374</v>
+        <v>10830114</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>61</v>
@@ -4164,7 +4164,7 @@
     </row>
     <row r="22" spans="1:41" customHeight="1" ht="60">
       <c r="A22" s="5">
-        <v>10755757</v>
+        <v>10933681</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>62</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="23" spans="1:41" customHeight="1" ht="60">
       <c r="A23" s="7">
-        <v>10755771</v>
+        <v>10934923</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>63</v>
@@ -4414,7 +4414,7 @@
     </row>
     <row r="24" spans="1:41" customHeight="1" ht="60">
       <c r="A24" s="5">
-        <v>11031046</v>
+        <v>10217868</v>
       </c>
       <c r="B24" s="9" t="s">
         <v>64</v>
@@ -4539,7 +4539,7 @@
     </row>
     <row r="25" spans="1:41" customHeight="1" ht="60">
       <c r="A25" s="7">
-        <v>11031060</v>
+        <v>10751337</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>65</v>
@@ -4664,7 +4664,7 @@
     </row>
     <row r="26" spans="1:41" customHeight="1" ht="60">
       <c r="A26" s="5">
-        <v>10937304</v>
+        <v>10937278</v>
       </c>
       <c r="B26" s="9" t="s">
         <v>66</v>
@@ -4789,7 +4789,7 @@
     </row>
     <row r="27" spans="1:41" customHeight="1" ht="60">
       <c r="A27" s="7">
-        <v>10937419</v>
+        <v>10937365</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>67</v>
@@ -8341,7 +8341,7 @@
       </c>
       <c r="C17" s="16"/>
     </row>
-    <row r="18" spans="1:3" customHeight="1" ht="51">
+    <row r="18" spans="1:3" customHeight="1" ht="25.5">
       <c r="A18" s="13" t="s">
         <v>98</v>
       </c>
